--- a/寄存器分配与协议new.xlsx
+++ b/寄存器分配与协议new.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\021_dehumi_analog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF4124BB-8A5A-4B0F-BA83-9A4FC34353BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FDE2C38-8FF2-478D-8C16-D5E3DB2CA140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="462">
   <si>
     <t>寄存器分配表</t>
   </si>
@@ -1450,6 +1450,22 @@
   </si>
   <si>
     <t>bool</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>排水頁初始化</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动排水按钮</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>定时开关</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>设置定时任务</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1499,7 +1515,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1539,6 +1555,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1655,7 +1677,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1885,6 +1907,22 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1897,6 +1935,10 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -1905,69 +1947,61 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1983,16 +2017,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -2319,7 +2353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H137"/>
+  <dimension ref="A1:H138"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="13.46484375" style="39" customWidth="1"/>
@@ -2334,24 +2368,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A2" s="70"/>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" s="23" t="s">
@@ -2375,7 +2409,7 @@
       <c r="G3" s="23"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A4" s="65" t="s">
+      <c r="A4" s="69" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="23">
@@ -2391,12 +2425,12 @@
         <v>10</v>
       </c>
       <c r="F4" s="23"/>
-      <c r="G4" s="65" t="s">
+      <c r="G4" s="69" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A5" s="66"/>
+      <c r="A5" s="70"/>
       <c r="B5" s="23">
         <v>1</v>
       </c>
@@ -2412,10 +2446,10 @@
       <c r="F5" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="66"/>
+      <c r="G5" s="70"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A6" s="66"/>
+      <c r="A6" s="70"/>
       <c r="B6" s="23">
         <v>2</v>
       </c>
@@ -2431,10 +2465,10 @@
       <c r="F6" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="66"/>
+      <c r="G6" s="70"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A7" s="66"/>
+      <c r="A7" s="70"/>
       <c r="B7" s="23">
         <v>3</v>
       </c>
@@ -2450,10 +2484,10 @@
       <c r="F7" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="66"/>
+      <c r="G7" s="70"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A8" s="66"/>
+      <c r="A8" s="70"/>
       <c r="B8" s="23">
         <v>4</v>
       </c>
@@ -2467,10 +2501,10 @@
         <v>10</v>
       </c>
       <c r="F8" s="23"/>
-      <c r="G8" s="66"/>
+      <c r="G8" s="70"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A9" s="66"/>
+      <c r="A9" s="70"/>
       <c r="B9" s="23">
         <v>5</v>
       </c>
@@ -2486,10 +2520,10 @@
       <c r="F9" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="G9" s="66"/>
+      <c r="G9" s="70"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A10" s="66"/>
+      <c r="A10" s="70"/>
       <c r="B10" s="63">
         <v>6</v>
       </c>
@@ -2505,13 +2539,13 @@
       <c r="F10" s="63" t="s">
         <v>452</v>
       </c>
-      <c r="G10" s="66"/>
+      <c r="G10" s="70"/>
       <c r="H10" s="41" t="s">
         <v>453</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="27.75" x14ac:dyDescent="0.4">
-      <c r="A11" s="66"/>
+      <c r="A11" s="70"/>
       <c r="B11" s="63">
         <v>7</v>
       </c>
@@ -2525,13 +2559,13 @@
         <v>18</v>
       </c>
       <c r="F11" s="63"/>
-      <c r="G11" s="66"/>
+      <c r="G11" s="70"/>
       <c r="H11" s="41" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A12" s="66"/>
+      <c r="A12" s="70"/>
       <c r="B12" s="23">
         <v>8</v>
       </c>
@@ -2545,10 +2579,10 @@
         <v>10</v>
       </c>
       <c r="F12" s="23"/>
-      <c r="G12" s="66"/>
+      <c r="G12" s="70"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A13" s="66"/>
+      <c r="A13" s="70"/>
       <c r="B13" s="23">
         <v>9</v>
       </c>
@@ -2562,10 +2596,10 @@
         <v>10</v>
       </c>
       <c r="F13" s="23"/>
-      <c r="G13" s="66"/>
+      <c r="G13" s="70"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A14" s="66"/>
+      <c r="A14" s="70"/>
       <c r="B14" s="23">
         <v>10</v>
       </c>
@@ -2579,10 +2613,10 @@
         <v>10</v>
       </c>
       <c r="F14" s="23"/>
-      <c r="G14" s="66"/>
+      <c r="G14" s="70"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A15" s="66"/>
+      <c r="A15" s="70"/>
       <c r="B15" s="23">
         <v>11</v>
       </c>
@@ -2596,19 +2630,19 @@
         <v>10</v>
       </c>
       <c r="F15" s="23"/>
-      <c r="G15" s="66"/>
+      <c r="G15" s="70"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A16" s="66"/>
+      <c r="A16" s="70"/>
       <c r="B16" s="23"/>
       <c r="C16" s="23"/>
       <c r="D16" s="23"/>
       <c r="E16" s="23"/>
       <c r="F16" s="23"/>
-      <c r="G16" s="66"/>
+      <c r="G16" s="70"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A17" s="66"/>
+      <c r="A17" s="70"/>
       <c r="B17" s="23">
         <v>50</v>
       </c>
@@ -2620,40 +2654,40 @@
         <v>19</v>
       </c>
       <c r="F17" s="23"/>
-      <c r="G17" s="66"/>
+      <c r="G17" s="70"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A18" s="66"/>
+      <c r="A18" s="70"/>
       <c r="F18" s="23"/>
-      <c r="G18" s="66"/>
+      <c r="G18" s="70"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A19" s="66"/>
+      <c r="A19" s="70"/>
       <c r="B19" s="23"/>
       <c r="C19" s="23"/>
       <c r="D19" s="23"/>
       <c r="E19" s="23"/>
       <c r="F19" s="23"/>
-      <c r="G19" s="66"/>
+      <c r="G19" s="70"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A20" s="67"/>
+      <c r="A20" s="71"/>
       <c r="B20" s="23"/>
       <c r="C20" s="23"/>
       <c r="D20" s="23"/>
       <c r="E20" s="23"/>
       <c r="F20" s="23"/>
-      <c r="G20" s="67"/>
+      <c r="G20" s="71"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A21" s="70" t="s">
+      <c r="A21" s="78" t="s">
         <v>20</v>
       </c>
       <c r="B21" s="23">
         <v>100</v>
       </c>
       <c r="C21" s="23">
-        <f>B21</f>
+        <f t="shared" ref="C21:C29" si="0">B21</f>
         <v>100</v>
       </c>
       <c r="D21" s="23"/>
@@ -2663,18 +2697,18 @@
       <c r="F21" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="G21" s="68" t="s">
+      <c r="G21" s="73" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A22" s="70"/>
+      <c r="A22" s="78"/>
       <c r="B22" s="23">
-        <f>C21+1</f>
+        <f t="shared" ref="B22:B29" si="1">C21+1</f>
         <v>101</v>
       </c>
       <c r="C22" s="23">
-        <f>B22</f>
+        <f t="shared" si="0"/>
         <v>101</v>
       </c>
       <c r="D22" s="23"/>
@@ -2684,16 +2718,16 @@
       <c r="F22" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="G22" s="68"/>
+      <c r="G22" s="73"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A23" s="70"/>
+      <c r="A23" s="78"/>
       <c r="B23" s="23">
-        <f>C22+1</f>
+        <f t="shared" si="1"/>
         <v>102</v>
       </c>
       <c r="C23" s="23">
-        <f>B23</f>
+        <f t="shared" si="0"/>
         <v>102</v>
       </c>
       <c r="D23" s="23"/>
@@ -2703,16 +2737,16 @@
       <c r="F23" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="G23" s="68"/>
+      <c r="G23" s="73"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A24" s="70"/>
+      <c r="A24" s="78"/>
       <c r="B24" s="23">
-        <f>C23+1</f>
+        <f t="shared" si="1"/>
         <v>103</v>
       </c>
       <c r="C24" s="23">
-        <f>B24</f>
+        <f t="shared" si="0"/>
         <v>103</v>
       </c>
       <c r="D24" s="42"/>
@@ -2722,16 +2756,16 @@
       <c r="F24" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="G24" s="68"/>
+      <c r="G24" s="73"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A25" s="70"/>
+      <c r="A25" s="78"/>
       <c r="B25" s="23">
-        <f>C24+1</f>
+        <f t="shared" si="1"/>
         <v>104</v>
       </c>
       <c r="C25" s="23">
-        <f>B25</f>
+        <f t="shared" si="0"/>
         <v>104</v>
       </c>
       <c r="D25" s="23"/>
@@ -2741,16 +2775,16 @@
       <c r="F25" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="G25" s="68"/>
+      <c r="G25" s="73"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A26" s="70"/>
+      <c r="A26" s="78"/>
       <c r="B26" s="23">
-        <f>C25+1</f>
+        <f t="shared" si="1"/>
         <v>105</v>
       </c>
       <c r="C26" s="23">
-        <f>B26</f>
+        <f t="shared" si="0"/>
         <v>105</v>
       </c>
       <c r="D26" s="23"/>
@@ -2760,16 +2794,16 @@
       <c r="F26" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="G26" s="68"/>
+      <c r="G26" s="73"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A27" s="70"/>
+      <c r="A27" s="78"/>
       <c r="B27" s="27">
-        <f>C26+1</f>
+        <f t="shared" si="1"/>
         <v>106</v>
       </c>
       <c r="C27" s="27">
-        <f>B27</f>
+        <f t="shared" si="0"/>
         <v>106</v>
       </c>
       <c r="D27" s="27"/>
@@ -2779,19 +2813,19 @@
       <c r="F27" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="G27" s="68"/>
+      <c r="G27" s="73"/>
       <c r="H27" s="41" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A28" s="70"/>
+      <c r="A28" s="78"/>
       <c r="B28" s="27">
-        <f>C27+1</f>
+        <f t="shared" si="1"/>
         <v>107</v>
       </c>
       <c r="C28" s="27">
-        <f>B28</f>
+        <f t="shared" si="0"/>
         <v>107</v>
       </c>
       <c r="D28" s="27"/>
@@ -2801,19 +2835,19 @@
       <c r="F28" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="G28" s="68"/>
+      <c r="G28" s="73"/>
       <c r="H28" s="41" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A29" s="70"/>
+      <c r="A29" s="78"/>
       <c r="B29" s="27">
-        <f>C28+1</f>
+        <f t="shared" si="1"/>
         <v>108</v>
       </c>
       <c r="C29" s="27">
-        <f>B29</f>
+        <f t="shared" si="0"/>
         <v>108</v>
       </c>
       <c r="D29" s="27"/>
@@ -2823,21 +2857,21 @@
       <c r="F29" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="G29" s="68"/>
+      <c r="G29" s="73"/>
       <c r="H29" s="41" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A30" s="70"/>
+      <c r="A30" s="78"/>
       <c r="B30" s="23"/>
       <c r="C30" s="23"/>
       <c r="D30" s="23"/>
       <c r="F30" s="23"/>
-      <c r="G30" s="68"/>
+      <c r="G30" s="73"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A31" s="70"/>
+      <c r="A31" s="78"/>
       <c r="B31" s="27">
         <v>120</v>
       </c>
@@ -2853,13 +2887,13 @@
       <c r="F31" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="G31" s="68"/>
+      <c r="G31" s="73"/>
       <c r="H31" s="41" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A32" s="70"/>
+      <c r="A32" s="78"/>
       <c r="B32" s="27">
         <v>122</v>
       </c>
@@ -2875,13 +2909,13 @@
       <c r="F32" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="G32" s="68"/>
+      <c r="G32" s="73"/>
       <c r="H32" s="41" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A33" s="70"/>
+      <c r="A33" s="78"/>
       <c r="B33" s="27">
         <v>123</v>
       </c>
@@ -2897,31 +2931,31 @@
       <c r="F33" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="G33" s="68"/>
+      <c r="G33" s="73"/>
       <c r="H33" s="41" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A34" s="70"/>
+      <c r="A34" s="78"/>
       <c r="B34" s="23"/>
       <c r="C34" s="23"/>
       <c r="D34" s="23"/>
       <c r="E34" s="23"/>
       <c r="F34" s="23"/>
-      <c r="G34" s="68"/>
+      <c r="G34" s="73"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A35" s="70"/>
+      <c r="A35" s="78"/>
       <c r="B35" s="42"/>
       <c r="C35" s="42"/>
       <c r="D35" s="42"/>
       <c r="E35" s="42"/>
       <c r="F35" s="23"/>
-      <c r="G35" s="69"/>
+      <c r="G35" s="74"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A36" s="65" t="s">
+      <c r="A36" s="69" t="s">
         <v>38</v>
       </c>
       <c r="B36" s="27">
@@ -2937,10 +2971,10 @@
       <c r="E36" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="F36" s="65" t="s">
+      <c r="F36" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="G36" s="66" t="s">
+      <c r="G36" s="70" t="s">
         <v>41</v>
       </c>
       <c r="H36" s="41" t="s">
@@ -2948,9 +2982,9 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A37" s="66"/>
+      <c r="A37" s="70"/>
       <c r="B37" s="23">
-        <f>C36+1</f>
+        <f t="shared" ref="B37:B60" si="2">C36+1</f>
         <v>302</v>
       </c>
       <c r="C37" s="23">
@@ -2963,16 +2997,16 @@
       <c r="E37" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F37" s="66"/>
-      <c r="G37" s="66"/>
+      <c r="F37" s="70"/>
+      <c r="G37" s="70"/>
       <c r="H37" s="41" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A38" s="66"/>
+      <c r="A38" s="70"/>
       <c r="B38" s="23">
-        <f>C37+1</f>
+        <f t="shared" si="2"/>
         <v>304</v>
       </c>
       <c r="C38" s="23">
@@ -2985,16 +3019,16 @@
       <c r="E38" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F38" s="66"/>
-      <c r="G38" s="66"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
       <c r="H38" s="41" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A39" s="66"/>
+      <c r="A39" s="70"/>
       <c r="B39" s="27">
-        <f>C38+1</f>
+        <f t="shared" si="2"/>
         <v>306</v>
       </c>
       <c r="C39" s="27">
@@ -3007,20 +3041,20 @@
       <c r="E39" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="F39" s="67"/>
-      <c r="G39" s="66"/>
+      <c r="F39" s="71"/>
+      <c r="G39" s="70"/>
       <c r="H39" s="41" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A40" s="66"/>
+      <c r="A40" s="70"/>
       <c r="B40" s="27">
-        <f>C39+1</f>
+        <f t="shared" si="2"/>
         <v>308</v>
       </c>
       <c r="C40" s="27">
-        <f>B40</f>
+        <f t="shared" ref="C40:C54" si="3">B40</f>
         <v>308</v>
       </c>
       <c r="D40" s="27" t="s">
@@ -3029,22 +3063,22 @@
       <c r="E40" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="F40" s="65" t="s">
+      <c r="F40" s="69" t="s">
         <v>46</v>
       </c>
-      <c r="G40" s="66"/>
+      <c r="G40" s="70"/>
       <c r="H40" s="41" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A41" s="66"/>
+      <c r="A41" s="70"/>
       <c r="B41" s="23">
-        <f>C40+1</f>
+        <f t="shared" si="2"/>
         <v>309</v>
       </c>
       <c r="C41" s="23">
-        <f>B41</f>
+        <f t="shared" si="3"/>
         <v>309</v>
       </c>
       <c r="D41" s="23" t="s">
@@ -3053,20 +3087,20 @@
       <c r="E41" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F41" s="66"/>
-      <c r="G41" s="66"/>
+      <c r="F41" s="70"/>
+      <c r="G41" s="70"/>
       <c r="H41" s="41" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A42" s="66"/>
+      <c r="A42" s="70"/>
       <c r="B42" s="23">
-        <f>C41+1</f>
+        <f t="shared" si="2"/>
         <v>310</v>
       </c>
       <c r="C42" s="23">
-        <f>B42</f>
+        <f t="shared" si="3"/>
         <v>310</v>
       </c>
       <c r="D42" s="23" t="s">
@@ -3075,20 +3109,20 @@
       <c r="E42" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F42" s="66"/>
-      <c r="G42" s="66"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
       <c r="H42" s="41" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A43" s="66"/>
+      <c r="A43" s="70"/>
       <c r="B43" s="27">
-        <f>C42+1</f>
+        <f t="shared" si="2"/>
         <v>311</v>
       </c>
       <c r="C43" s="27">
-        <f>B43</f>
+        <f t="shared" si="3"/>
         <v>311</v>
       </c>
       <c r="D43" s="27" t="s">
@@ -3097,20 +3131,20 @@
       <c r="E43" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="F43" s="67"/>
-      <c r="G43" s="66"/>
+      <c r="F43" s="71"/>
+      <c r="G43" s="70"/>
       <c r="H43" s="41" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A44" s="66"/>
+      <c r="A44" s="70"/>
       <c r="B44" s="23">
-        <f>C43+1</f>
+        <f t="shared" si="2"/>
         <v>312</v>
       </c>
       <c r="C44" s="23">
-        <f>B44</f>
+        <f t="shared" si="3"/>
         <v>312</v>
       </c>
       <c r="D44" s="23" t="s">
@@ -3119,19 +3153,19 @@
       <c r="E44" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F44" s="65" t="s">
+      <c r="F44" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="G44" s="66"/>
+      <c r="G44" s="70"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A45" s="66"/>
+      <c r="A45" s="70"/>
       <c r="B45" s="23">
-        <f>C44+1</f>
+        <f t="shared" si="2"/>
         <v>313</v>
       </c>
       <c r="C45" s="23">
-        <f>B45</f>
+        <f t="shared" si="3"/>
         <v>313</v>
       </c>
       <c r="D45" s="23" t="s">
@@ -3140,17 +3174,17 @@
       <c r="E45" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F45" s="67"/>
-      <c r="G45" s="66"/>
+      <c r="F45" s="71"/>
+      <c r="G45" s="70"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A46" s="66"/>
+      <c r="A46" s="70"/>
       <c r="B46" s="23">
-        <f>C45+1</f>
+        <f t="shared" si="2"/>
         <v>314</v>
       </c>
       <c r="C46" s="23">
-        <f>B46</f>
+        <f t="shared" si="3"/>
         <v>314</v>
       </c>
       <c r="D46" s="23" t="s">
@@ -3159,19 +3193,19 @@
       <c r="E46" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F46" s="65" t="s">
+      <c r="F46" s="69" t="s">
         <v>51</v>
       </c>
-      <c r="G46" s="66"/>
+      <c r="G46" s="70"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A47" s="66"/>
+      <c r="A47" s="70"/>
       <c r="B47" s="23">
-        <f>C46+1</f>
+        <f t="shared" si="2"/>
         <v>315</v>
       </c>
       <c r="C47" s="23">
-        <f>B47</f>
+        <f t="shared" si="3"/>
         <v>315</v>
       </c>
       <c r="D47" s="23" t="s">
@@ -3180,17 +3214,17 @@
       <c r="E47" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F47" s="67"/>
-      <c r="G47" s="66"/>
+      <c r="F47" s="71"/>
+      <c r="G47" s="70"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A48" s="66"/>
+      <c r="A48" s="70"/>
       <c r="B48" s="27">
-        <f>C47+1</f>
+        <f t="shared" si="2"/>
         <v>316</v>
       </c>
       <c r="C48" s="27">
-        <f>B48</f>
+        <f t="shared" si="3"/>
         <v>316</v>
       </c>
       <c r="D48" s="27" t="s">
@@ -3202,19 +3236,19 @@
       <c r="F48" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="G48" s="66"/>
+      <c r="G48" s="70"/>
       <c r="H48" s="41" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A49" s="66"/>
+      <c r="A49" s="70"/>
       <c r="B49" s="27">
-        <f>C48+1</f>
+        <f t="shared" si="2"/>
         <v>317</v>
       </c>
       <c r="C49" s="27">
-        <f>B49</f>
+        <f t="shared" si="3"/>
         <v>317</v>
       </c>
       <c r="D49" s="43" t="s">
@@ -3223,22 +3257,22 @@
       <c r="E49" s="54" t="s">
         <v>442</v>
       </c>
-      <c r="F49" s="65" t="s">
+      <c r="F49" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="G49" s="66"/>
+      <c r="G49" s="70"/>
       <c r="H49" s="41" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A50" s="66"/>
+      <c r="A50" s="70"/>
       <c r="B50" s="23">
-        <f>C49+1</f>
+        <f t="shared" si="2"/>
         <v>318</v>
       </c>
       <c r="C50" s="23">
-        <f>B50</f>
+        <f t="shared" si="3"/>
         <v>318</v>
       </c>
       <c r="D50" s="23" t="s">
@@ -3247,17 +3281,17 @@
       <c r="E50" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F50" s="67"/>
-      <c r="G50" s="66"/>
+      <c r="F50" s="71"/>
+      <c r="G50" s="70"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A51" s="66"/>
+      <c r="A51" s="70"/>
       <c r="B51" s="23">
-        <f>C50+1</f>
+        <f t="shared" si="2"/>
         <v>319</v>
       </c>
       <c r="C51" s="23">
-        <f>B51</f>
+        <f t="shared" si="3"/>
         <v>319</v>
       </c>
       <c r="D51" s="23" t="s">
@@ -3266,20 +3300,20 @@
       <c r="E51" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F51" s="65" t="s">
-        <v>8</v>
-      </c>
-      <c r="G51" s="66"/>
+      <c r="F51" s="69" t="s">
+        <v>8</v>
+      </c>
+      <c r="G51" s="70"/>
       <c r="H51" s="44"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A52" s="66"/>
+      <c r="A52" s="70"/>
       <c r="B52" s="23">
-        <f>C51+1</f>
+        <f t="shared" si="2"/>
         <v>320</v>
       </c>
       <c r="C52" s="23">
-        <f>B52</f>
+        <f t="shared" si="3"/>
         <v>320</v>
       </c>
       <c r="D52" s="23" t="s">
@@ -3288,18 +3322,18 @@
       <c r="E52" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F52" s="66"/>
-      <c r="G52" s="66"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
       <c r="H52" s="44"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A53" s="66"/>
+      <c r="A53" s="70"/>
       <c r="B53" s="23">
-        <f>C52+1</f>
+        <f t="shared" si="2"/>
         <v>321</v>
       </c>
       <c r="C53" s="23">
-        <f>B53</f>
+        <f t="shared" si="3"/>
         <v>321</v>
       </c>
       <c r="D53" s="23" t="s">
@@ -3308,18 +3342,18 @@
       <c r="E53" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F53" s="66"/>
-      <c r="G53" s="66"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
       <c r="H53" s="44"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A54" s="66"/>
+      <c r="A54" s="70"/>
       <c r="B54" s="23">
-        <f>C53+1</f>
+        <f t="shared" si="2"/>
         <v>322</v>
       </c>
       <c r="C54" s="23">
-        <f>B54</f>
+        <f t="shared" si="3"/>
         <v>322</v>
       </c>
       <c r="D54" s="23" t="s">
@@ -3328,13 +3362,13 @@
       <c r="E54" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F54" s="66"/>
-      <c r="G54" s="66"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A55" s="66"/>
+      <c r="A55" s="70"/>
       <c r="B55" s="23">
-        <f>C54+1</f>
+        <f t="shared" si="2"/>
         <v>323</v>
       </c>
       <c r="C55" s="23">
@@ -3347,13 +3381,13 @@
       <c r="E55" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F55" s="67"/>
-      <c r="G55" s="66"/>
+      <c r="F55" s="71"/>
+      <c r="G55" s="70"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A56" s="66"/>
+      <c r="A56" s="70"/>
       <c r="B56" s="23">
-        <f>C55+1</f>
+        <f t="shared" si="2"/>
         <v>325</v>
       </c>
       <c r="C56" s="23">
@@ -3369,12 +3403,12 @@
       <c r="F56" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="G56" s="66"/>
+      <c r="G56" s="70"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A57" s="66"/>
+      <c r="A57" s="70"/>
       <c r="B57" s="23">
-        <f>C56+1</f>
+        <f t="shared" si="2"/>
         <v>326</v>
       </c>
       <c r="C57" s="23">
@@ -3387,13 +3421,13 @@
       <c r="E57" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="68"/>
-      <c r="G57" s="66"/>
+      <c r="F57" s="73"/>
+      <c r="G57" s="70"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A58" s="66"/>
+      <c r="A58" s="70"/>
       <c r="B58" s="23">
-        <f>C57+1</f>
+        <f t="shared" si="2"/>
         <v>327</v>
       </c>
       <c r="C58" s="23">
@@ -3406,13 +3440,13 @@
       <c r="E58" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F58" s="68"/>
-      <c r="G58" s="66"/>
+      <c r="F58" s="73"/>
+      <c r="G58" s="70"/>
     </row>
     <row r="59" spans="1:8" ht="27.75" x14ac:dyDescent="0.4">
-      <c r="A59" s="66"/>
+      <c r="A59" s="70"/>
       <c r="B59" s="23">
-        <f>C58+1</f>
+        <f t="shared" si="2"/>
         <v>328</v>
       </c>
       <c r="C59" s="23">
@@ -3425,17 +3459,17 @@
       <c r="E59" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="F59" s="69"/>
-      <c r="G59" s="66"/>
+      <c r="F59" s="74"/>
+      <c r="G59" s="70"/>
     </row>
     <row r="60" spans="1:8" ht="27.75" x14ac:dyDescent="0.4">
-      <c r="A60" s="66"/>
+      <c r="A60" s="70"/>
       <c r="B60" s="27">
-        <f>C59+1</f>
+        <f t="shared" si="2"/>
         <v>330</v>
       </c>
       <c r="C60" s="27">
-        <f>B60</f>
+        <f t="shared" ref="C60:C76" si="4">B60</f>
         <v>330</v>
       </c>
       <c r="D60" s="27" t="s">
@@ -3447,18 +3481,18 @@
       <c r="F60" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="G60" s="66"/>
+      <c r="G60" s="70"/>
       <c r="H60" s="41" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A61" s="66"/>
+      <c r="A61" s="70"/>
       <c r="B61" s="27">
         <v>331</v>
       </c>
       <c r="C61" s="27">
-        <f>B61</f>
+        <f t="shared" si="4"/>
         <v>331</v>
       </c>
       <c r="D61" s="27" t="s">
@@ -3470,18 +3504,18 @@
       <c r="F61" s="72" t="s">
         <v>65</v>
       </c>
-      <c r="G61" s="66"/>
+      <c r="G61" s="70"/>
       <c r="H61" s="41" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A62" s="66"/>
+      <c r="A62" s="70"/>
       <c r="B62" s="27">
         <v>332</v>
       </c>
       <c r="C62" s="27">
-        <f>B62</f>
+        <f t="shared" si="4"/>
         <v>332</v>
       </c>
       <c r="D62" s="27" t="s">
@@ -3490,19 +3524,19 @@
       <c r="E62" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="F62" s="68"/>
-      <c r="G62" s="66"/>
+      <c r="F62" s="73"/>
+      <c r="G62" s="70"/>
       <c r="H62" s="41" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A63" s="66"/>
+      <c r="A63" s="70"/>
       <c r="B63" s="27">
         <v>333</v>
       </c>
       <c r="C63" s="27">
-        <f>B63</f>
+        <f t="shared" si="4"/>
         <v>333</v>
       </c>
       <c r="D63" s="27" t="s">
@@ -3511,19 +3545,19 @@
       <c r="E63" s="37" t="s">
         <v>69</v>
       </c>
-      <c r="F63" s="68"/>
-      <c r="G63" s="66"/>
+      <c r="F63" s="73"/>
+      <c r="G63" s="70"/>
       <c r="H63" s="41" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A64" s="66"/>
+      <c r="A64" s="70"/>
       <c r="B64" s="23">
         <v>334</v>
       </c>
       <c r="C64" s="23">
-        <f>B64</f>
+        <f t="shared" si="4"/>
         <v>334</v>
       </c>
       <c r="D64" s="23" t="s">
@@ -3532,16 +3566,16 @@
       <c r="E64" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="F64" s="69"/>
-      <c r="G64" s="66"/>
+      <c r="F64" s="74"/>
+      <c r="G64" s="70"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A65" s="66"/>
+      <c r="A65" s="70"/>
       <c r="B65" s="23">
         <v>335</v>
       </c>
       <c r="C65" s="23">
-        <f>B65</f>
+        <f t="shared" si="4"/>
         <v>335</v>
       </c>
       <c r="D65" s="39" t="s">
@@ -3551,18 +3585,18 @@
         <v>8</v>
       </c>
       <c r="F65" s="34"/>
-      <c r="G65" s="66"/>
+      <c r="G65" s="70"/>
       <c r="H65" s="41" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="27.75" x14ac:dyDescent="0.4">
-      <c r="A66" s="66"/>
+      <c r="A66" s="70"/>
       <c r="B66" s="27">
         <v>336</v>
       </c>
       <c r="C66" s="27">
-        <f>B66</f>
+        <f t="shared" si="4"/>
         <v>336</v>
       </c>
       <c r="D66" s="27" t="s">
@@ -3572,18 +3606,18 @@
         <v>71</v>
       </c>
       <c r="F66" s="34"/>
-      <c r="G66" s="66"/>
+      <c r="G66" s="70"/>
       <c r="H66" s="45" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A67" s="66"/>
+      <c r="A67" s="70"/>
       <c r="B67" s="29">
         <v>337</v>
       </c>
       <c r="C67" s="29">
-        <f>B67</f>
+        <f t="shared" si="4"/>
         <v>337</v>
       </c>
       <c r="D67" s="29" t="s">
@@ -3592,21 +3626,21 @@
       <c r="E67" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="F67" s="73" t="s">
+      <c r="F67" s="75" t="s">
         <v>74</v>
       </c>
-      <c r="G67" s="66"/>
+      <c r="G67" s="70"/>
       <c r="H67" s="44" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A68" s="66"/>
+      <c r="A68" s="70"/>
       <c r="B68" s="29">
         <v>338</v>
       </c>
       <c r="C68" s="29">
-        <f>B68</f>
+        <f t="shared" si="4"/>
         <v>338</v>
       </c>
       <c r="D68" s="29" t="s">
@@ -3615,19 +3649,19 @@
       <c r="E68" s="46" t="s">
         <v>76</v>
       </c>
-      <c r="F68" s="74"/>
-      <c r="G68" s="66"/>
+      <c r="F68" s="76"/>
+      <c r="G68" s="70"/>
       <c r="H68" s="44" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A69" s="66"/>
+      <c r="A69" s="70"/>
       <c r="B69" s="29">
         <v>339</v>
       </c>
       <c r="C69" s="29">
-        <f>B69</f>
+        <f t="shared" si="4"/>
         <v>339</v>
       </c>
       <c r="D69" s="29" t="s">
@@ -3636,19 +3670,19 @@
       <c r="E69" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="F69" s="74"/>
-      <c r="G69" s="66"/>
+      <c r="F69" s="76"/>
+      <c r="G69" s="70"/>
       <c r="H69" s="44" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A70" s="66"/>
+      <c r="A70" s="70"/>
       <c r="B70" s="29">
         <v>340</v>
       </c>
       <c r="C70" s="29">
-        <f>B70</f>
+        <f t="shared" si="4"/>
         <v>340</v>
       </c>
       <c r="D70" s="29" t="s">
@@ -3657,19 +3691,19 @@
       <c r="E70" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="F70" s="74"/>
-      <c r="G70" s="66"/>
+      <c r="F70" s="76"/>
+      <c r="G70" s="70"/>
       <c r="H70" s="44" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A71" s="66"/>
+      <c r="A71" s="70"/>
       <c r="B71" s="29">
         <v>341</v>
       </c>
       <c r="C71" s="29">
-        <f>B71</f>
+        <f t="shared" si="4"/>
         <v>341</v>
       </c>
       <c r="D71" s="29" t="s">
@@ -3678,19 +3712,19 @@
       <c r="E71" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="F71" s="74"/>
-      <c r="G71" s="66"/>
+      <c r="F71" s="76"/>
+      <c r="G71" s="70"/>
       <c r="H71" s="44" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A72" s="66"/>
+      <c r="A72" s="70"/>
       <c r="B72" s="29">
         <v>342</v>
       </c>
       <c r="C72" s="29">
-        <f>B72</f>
+        <f t="shared" si="4"/>
         <v>342</v>
       </c>
       <c r="D72" s="29" t="s">
@@ -3699,19 +3733,19 @@
       <c r="E72" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="F72" s="74"/>
-      <c r="G72" s="66"/>
+      <c r="F72" s="76"/>
+      <c r="G72" s="70"/>
       <c r="H72" s="44" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A73" s="66"/>
+      <c r="A73" s="70"/>
       <c r="B73" s="29">
         <v>343</v>
       </c>
       <c r="C73" s="29">
-        <f>B73</f>
+        <f t="shared" si="4"/>
         <v>343</v>
       </c>
       <c r="D73" s="29" t="s">
@@ -3720,19 +3754,19 @@
       <c r="E73" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="F73" s="74"/>
-      <c r="G73" s="66"/>
+      <c r="F73" s="76"/>
+      <c r="G73" s="70"/>
       <c r="H73" s="44" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A74" s="66"/>
+      <c r="A74" s="70"/>
       <c r="B74" s="29">
         <v>344</v>
       </c>
       <c r="C74" s="29">
-        <f>B74</f>
+        <f t="shared" si="4"/>
         <v>344</v>
       </c>
       <c r="D74" s="29" t="s">
@@ -3741,19 +3775,19 @@
       <c r="E74" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="F74" s="74"/>
-      <c r="G74" s="66"/>
+      <c r="F74" s="76"/>
+      <c r="G74" s="70"/>
       <c r="H74" s="44" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A75" s="66"/>
+      <c r="A75" s="70"/>
       <c r="B75" s="29">
         <v>345</v>
       </c>
       <c r="C75" s="29">
-        <f>B75</f>
+        <f t="shared" si="4"/>
         <v>345</v>
       </c>
       <c r="D75" s="29" t="s">
@@ -3762,19 +3796,19 @@
       <c r="E75" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="F75" s="74"/>
-      <c r="G75" s="66"/>
+      <c r="F75" s="76"/>
+      <c r="G75" s="70"/>
       <c r="H75" s="44" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A76" s="66"/>
+      <c r="A76" s="70"/>
       <c r="B76" s="29">
         <v>346</v>
       </c>
       <c r="C76" s="29">
-        <f>B76</f>
+        <f t="shared" si="4"/>
         <v>346</v>
       </c>
       <c r="D76" s="29" t="s">
@@ -3783,14 +3817,14 @@
       <c r="E76" s="46" t="s">
         <v>92</v>
       </c>
-      <c r="F76" s="75"/>
-      <c r="G76" s="66"/>
+      <c r="F76" s="77"/>
+      <c r="G76" s="70"/>
       <c r="H76" s="44" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="27.75" x14ac:dyDescent="0.4">
-      <c r="A77" s="66"/>
+      <c r="A77" s="70"/>
       <c r="B77" s="27">
         <v>347</v>
       </c>
@@ -3804,13 +3838,13 @@
         <v>94</v>
       </c>
       <c r="F77" s="34"/>
-      <c r="G77" s="66"/>
+      <c r="G77" s="70"/>
       <c r="H77" s="8" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A78" s="66"/>
+      <c r="A78" s="70"/>
       <c r="B78" s="48">
         <v>503</v>
       </c>
@@ -3825,13 +3859,13 @@
         <v>96</v>
       </c>
       <c r="F78" s="34"/>
-      <c r="G78" s="66"/>
+      <c r="G78" s="70"/>
       <c r="H78" s="45" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A79" s="66"/>
+      <c r="A79" s="70"/>
       <c r="B79" s="48">
         <f>C78+1</f>
         <v>505</v>
@@ -3847,13 +3881,13 @@
         <v>98</v>
       </c>
       <c r="F79" s="34"/>
-      <c r="G79" s="66"/>
+      <c r="G79" s="70"/>
       <c r="H79" s="45" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A80" s="66"/>
+      <c r="A80" s="70"/>
       <c r="B80" s="48">
         <v>507</v>
       </c>
@@ -3867,13 +3901,13 @@
         <v>100</v>
       </c>
       <c r="F80" s="34"/>
-      <c r="G80" s="66"/>
+      <c r="G80" s="70"/>
       <c r="H80" s="41" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A81" s="66"/>
+      <c r="A81" s="70"/>
       <c r="B81" s="48">
         <v>508</v>
       </c>
@@ -3887,13 +3921,13 @@
         <v>102</v>
       </c>
       <c r="F81" s="34"/>
-      <c r="G81" s="66"/>
+      <c r="G81" s="70"/>
       <c r="H81" s="41" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A82" s="66"/>
+      <c r="A82" s="70"/>
       <c r="B82" s="48">
         <v>509</v>
       </c>
@@ -3907,13 +3941,13 @@
         <v>104</v>
       </c>
       <c r="F82" s="34"/>
-      <c r="G82" s="66"/>
+      <c r="G82" s="70"/>
       <c r="H82" s="41" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A83" s="66"/>
+      <c r="A83" s="70"/>
       <c r="B83" s="48">
         <v>510</v>
       </c>
@@ -3927,13 +3961,13 @@
         <v>106</v>
       </c>
       <c r="F83" s="34"/>
-      <c r="G83" s="66"/>
+      <c r="G83" s="70"/>
       <c r="H83" s="41" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="27.75" x14ac:dyDescent="0.4">
-      <c r="A84" s="66"/>
+      <c r="A84" s="70"/>
       <c r="B84" s="48">
         <v>511</v>
       </c>
@@ -3947,13 +3981,13 @@
         <v>109</v>
       </c>
       <c r="F84" s="34"/>
-      <c r="G84" s="66"/>
+      <c r="G84" s="70"/>
       <c r="H84" s="45" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A85" s="66"/>
+      <c r="A85" s="70"/>
       <c r="B85" s="48">
         <v>513</v>
       </c>
@@ -3967,13 +4001,13 @@
         <v>111</v>
       </c>
       <c r="F85" s="34"/>
-      <c r="G85" s="66"/>
+      <c r="G85" s="70"/>
       <c r="H85" s="41" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A86" s="66"/>
+      <c r="A86" s="70"/>
       <c r="B86" s="48">
         <v>514</v>
       </c>
@@ -3987,13 +4021,13 @@
         <v>113</v>
       </c>
       <c r="F86" s="34"/>
-      <c r="G86" s="66"/>
+      <c r="G86" s="70"/>
       <c r="H86" s="41" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A87" s="66"/>
+      <c r="A87" s="70"/>
       <c r="B87" s="48">
         <v>515</v>
       </c>
@@ -4007,13 +4041,13 @@
         <v>115</v>
       </c>
       <c r="F87" s="34"/>
-      <c r="G87" s="66"/>
+      <c r="G87" s="70"/>
       <c r="H87" s="41" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="27.75" x14ac:dyDescent="0.4">
-      <c r="A88" s="66"/>
+      <c r="A88" s="70"/>
       <c r="B88" s="48">
         <v>516</v>
       </c>
@@ -4027,13 +4061,13 @@
         <v>117</v>
       </c>
       <c r="F88" s="34"/>
-      <c r="G88" s="66"/>
+      <c r="G88" s="70"/>
       <c r="H88" s="41" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A89" s="66"/>
+      <c r="A89" s="70"/>
       <c r="B89" s="48">
         <v>518</v>
       </c>
@@ -4047,13 +4081,13 @@
         <v>119</v>
       </c>
       <c r="F89" s="34"/>
-      <c r="G89" s="66"/>
+      <c r="G89" s="70"/>
       <c r="H89" s="41" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A90" s="66"/>
+      <c r="A90" s="70"/>
       <c r="B90" s="49">
         <v>519</v>
       </c>
@@ -4067,13 +4101,13 @@
         <v>121</v>
       </c>
       <c r="F90" s="34"/>
-      <c r="G90" s="66"/>
+      <c r="G90" s="70"/>
       <c r="H90" s="41" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A91" s="66"/>
+      <c r="A91" s="70"/>
       <c r="B91" s="49">
         <v>550</v>
       </c>
@@ -4087,10 +4121,10 @@
         <v>451</v>
       </c>
       <c r="F91" s="34"/>
-      <c r="G91" s="66"/>
+      <c r="G91" s="70"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A92" s="66"/>
+      <c r="A92" s="70"/>
       <c r="B92" s="23">
         <v>600</v>
       </c>
@@ -4104,10 +4138,10 @@
         <v>441</v>
       </c>
       <c r="F92" s="34"/>
-      <c r="G92" s="66"/>
+      <c r="G92" s="70"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A93" s="66"/>
+      <c r="A93" s="70"/>
       <c r="B93" s="49">
         <v>602</v>
       </c>
@@ -4121,31 +4155,31 @@
         <v>450</v>
       </c>
       <c r="F93" s="34"/>
-      <c r="G93" s="66"/>
+      <c r="G93" s="70"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A94" s="66"/>
+      <c r="A94" s="70"/>
       <c r="F94" s="34"/>
-      <c r="G94" s="66"/>
+      <c r="G94" s="70"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A95" s="67"/>
+      <c r="A95" s="71"/>
       <c r="B95" s="41"/>
       <c r="C95" s="41"/>
       <c r="D95" s="41"/>
       <c r="E95" s="41"/>
       <c r="F95" s="23"/>
-      <c r="G95" s="67"/>
+      <c r="G95" s="71"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A96" s="71" t="s">
+      <c r="A96" s="68" t="s">
         <v>123</v>
       </c>
       <c r="B96" s="52">
         <v>50000</v>
       </c>
       <c r="C96" s="23">
-        <f t="shared" ref="C96:C97" si="0">B96</f>
+        <f t="shared" ref="C96:C97" si="5">B96</f>
         <v>50000</v>
       </c>
       <c r="D96" s="23" t="s">
@@ -4160,13 +4194,13 @@
       <c r="G96" s="23"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A97" s="71"/>
+      <c r="A97" s="68"/>
       <c r="B97" s="52">
         <f>C96+1</f>
         <v>50001</v>
       </c>
       <c r="C97" s="23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>50001</v>
       </c>
       <c r="D97" s="23" t="s">
@@ -4181,7 +4215,7 @@
       <c r="G97" s="23"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A98" s="71"/>
+      <c r="A98" s="68"/>
       <c r="B98" s="48">
         <v>50002</v>
       </c>
@@ -4201,7 +4235,7 @@
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A99" s="71"/>
+      <c r="A99" s="68"/>
       <c r="B99" s="48">
         <v>50003</v>
       </c>
@@ -4224,7 +4258,7 @@
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A100" s="71"/>
+      <c r="A100" s="68"/>
       <c r="B100" s="48">
         <f>C99+1</f>
         <v>50005</v>
@@ -4248,7 +4282,7 @@
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A101" s="71"/>
+      <c r="A101" s="68"/>
       <c r="B101" s="48">
         <f>C100+1</f>
         <v>50007</v>
@@ -4270,13 +4304,13 @@
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A102" s="71"/>
+      <c r="A102" s="68"/>
       <c r="B102" s="48">
-        <f t="shared" ref="B102:B107" si="1">C101+1</f>
+        <f t="shared" ref="B102:B107" si="6">C101+1</f>
         <v>50008</v>
       </c>
       <c r="C102" s="27">
-        <f t="shared" ref="C102:C107" si="2">B102</f>
+        <f t="shared" ref="C102:C107" si="7">B102</f>
         <v>50008</v>
       </c>
       <c r="D102" s="27" t="s">
@@ -4292,13 +4326,13 @@
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A103" s="71"/>
+      <c r="A103" s="68"/>
       <c r="B103" s="48">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>50009</v>
       </c>
       <c r="C103" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>50009</v>
       </c>
       <c r="D103" s="27" t="s">
@@ -4314,13 +4348,13 @@
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A104" s="71"/>
+      <c r="A104" s="68"/>
       <c r="B104" s="48">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>50010</v>
       </c>
       <c r="C104" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>50010</v>
       </c>
       <c r="D104" s="27" t="s">
@@ -4336,9 +4370,9 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="27.75" x14ac:dyDescent="0.4">
-      <c r="A105" s="71"/>
+      <c r="A105" s="68"/>
       <c r="B105" s="48">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>50011</v>
       </c>
       <c r="C105" s="27">
@@ -4358,13 +4392,13 @@
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A106" s="71"/>
+      <c r="A106" s="68"/>
       <c r="B106" s="48">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>50013</v>
       </c>
       <c r="C106" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>50013</v>
       </c>
       <c r="D106" s="27" t="s">
@@ -4380,13 +4414,13 @@
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A107" s="71"/>
+      <c r="A107" s="68"/>
       <c r="B107" s="48">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>50014</v>
       </c>
       <c r="C107" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>50014</v>
       </c>
       <c r="D107" s="27" t="s">
@@ -4402,7 +4436,7 @@
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A108" s="71"/>
+      <c r="A108" s="68"/>
       <c r="B108" s="48">
         <v>50015</v>
       </c>
@@ -4422,7 +4456,7 @@
       </c>
     </row>
     <row r="109" spans="1:8" ht="27.75" x14ac:dyDescent="0.4">
-      <c r="A109" s="71"/>
+      <c r="A109" s="68"/>
       <c r="B109" s="48">
         <v>50016</v>
       </c>
@@ -4443,7 +4477,7 @@
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A110" s="71"/>
+      <c r="A110" s="68"/>
       <c r="B110" s="48">
         <v>50018</v>
       </c>
@@ -4463,7 +4497,7 @@
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A111" s="71"/>
+      <c r="A111" s="68"/>
       <c r="B111" s="49">
         <f>C110+1</f>
         <v>50019</v>
@@ -4485,7 +4519,7 @@
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A112" s="71"/>
+      <c r="A112" s="68"/>
       <c r="B112" s="48">
         <v>50020</v>
       </c>
@@ -4505,7 +4539,7 @@
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A113" s="71"/>
+      <c r="A113" s="68"/>
       <c r="B113" s="48">
         <v>50021</v>
       </c>
@@ -4525,7 +4559,7 @@
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A114" s="71"/>
+      <c r="A114" s="68"/>
       <c r="B114" s="48">
         <v>50022</v>
       </c>
@@ -4545,7 +4579,7 @@
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A115" s="71"/>
+      <c r="A115" s="68"/>
       <c r="B115" s="48">
         <v>50023</v>
       </c>
@@ -4565,7 +4599,7 @@
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A116" s="71"/>
+      <c r="A116" s="68"/>
       <c r="B116" s="48">
         <v>50024</v>
       </c>
@@ -4585,7 +4619,7 @@
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A117" s="71"/>
+      <c r="A117" s="68"/>
       <c r="B117" s="48">
         <v>50025</v>
       </c>
@@ -4605,7 +4639,7 @@
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A118" s="71"/>
+      <c r="A118" s="68"/>
       <c r="B118" s="48">
         <v>50026</v>
       </c>
@@ -4625,7 +4659,7 @@
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A119" s="71"/>
+      <c r="A119" s="68"/>
       <c r="B119" s="48">
         <v>50027</v>
       </c>
@@ -4645,7 +4679,7 @@
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A120" s="71"/>
+      <c r="A120" s="68"/>
       <c r="B120" s="48">
         <v>50028</v>
       </c>
@@ -4665,7 +4699,7 @@
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A121" s="71"/>
+      <c r="A121" s="68"/>
       <c r="B121" s="48">
         <v>50029</v>
       </c>
@@ -4685,7 +4719,7 @@
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A122" s="71"/>
+      <c r="A122" s="68"/>
       <c r="B122" s="48">
         <v>50030</v>
       </c>
@@ -4705,7 +4739,7 @@
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A123" s="71"/>
+      <c r="A123" s="68"/>
       <c r="B123" s="48">
         <v>50031</v>
       </c>
@@ -4725,7 +4759,7 @@
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A124" s="71"/>
+      <c r="A124" s="68"/>
       <c r="B124" s="48">
         <v>50032</v>
       </c>
@@ -4745,7 +4779,7 @@
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A125" s="71"/>
+      <c r="A125" s="68"/>
       <c r="B125" s="48">
         <v>50033</v>
       </c>
@@ -4765,7 +4799,7 @@
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A126" s="71"/>
+      <c r="A126" s="68"/>
       <c r="B126" s="48">
         <v>50034</v>
       </c>
@@ -4785,7 +4819,7 @@
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A127" s="71"/>
+      <c r="A127" s="68"/>
       <c r="B127" s="48">
         <v>50035</v>
       </c>
@@ -4805,7 +4839,7 @@
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A128" s="71"/>
+      <c r="A128" s="68"/>
       <c r="B128" s="48">
         <v>50036</v>
       </c>
@@ -4825,7 +4859,7 @@
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A129" s="71"/>
+      <c r="A129" s="68"/>
       <c r="B129" s="48">
         <v>50037</v>
       </c>
@@ -4845,7 +4879,7 @@
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A130" s="71"/>
+      <c r="A130" s="68"/>
       <c r="B130" s="48">
         <v>50038</v>
       </c>
@@ -4884,7 +4918,7 @@
         <v>50051</v>
       </c>
       <c r="C132" s="27">
-        <f t="shared" ref="C132" si="3">B132</f>
+        <f t="shared" ref="C132" si="8">B132</f>
         <v>50051</v>
       </c>
       <c r="D132" s="27" t="s">
@@ -4899,7 +4933,7 @@
         <v>50052</v>
       </c>
       <c r="C133" s="27">
-        <f t="shared" ref="C133" si="4">B133</f>
+        <f t="shared" ref="C133" si="9">B133</f>
         <v>50052</v>
       </c>
       <c r="D133" s="27" t="s">
@@ -4937,37 +4971,61 @@
       <c r="G135" s="61"/>
       <c r="H135" s="62"/>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B136" s="39">
-        <v>51000</v>
-      </c>
-      <c r="C136" s="39">
-        <v>51000</v>
+    <row r="136" spans="1:8" s="98" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A136" s="97"/>
+      <c r="B136" s="97">
+        <v>50070</v>
+      </c>
+      <c r="C136" s="97">
+        <v>50070</v>
       </c>
       <c r="D136" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="E136" s="57" t="s">
-        <v>455</v>
-      </c>
+      <c r="E136" s="99" t="s">
+        <v>460</v>
+      </c>
+      <c r="F136" s="97"/>
+      <c r="G136" s="97"/>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B137" s="39">
-        <v>60002</v>
+        <v>51000</v>
       </c>
       <c r="C137" s="39">
-        <v>60002</v>
+        <v>51000</v>
       </c>
       <c r="D137" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="E137" s="58" t="s">
+      <c r="E137" s="57" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B138" s="39">
+        <v>60002</v>
+      </c>
+      <c r="C138" s="39">
+        <v>60002</v>
+      </c>
+      <c r="D138" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="E138" s="58" t="s">
         <v>450</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="17">
+    <mergeCell ref="G4:G20"/>
+    <mergeCell ref="G21:G35"/>
+    <mergeCell ref="G36:G95"/>
+    <mergeCell ref="A1:G2"/>
+    <mergeCell ref="A4:A20"/>
+    <mergeCell ref="A21:A35"/>
+    <mergeCell ref="A36:A95"/>
     <mergeCell ref="A96:A130"/>
     <mergeCell ref="F36:F39"/>
     <mergeCell ref="F40:F43"/>
@@ -4978,13 +5036,6 @@
     <mergeCell ref="F56:F59"/>
     <mergeCell ref="F61:F64"/>
     <mergeCell ref="F67:F76"/>
-    <mergeCell ref="G4:G20"/>
-    <mergeCell ref="G21:G35"/>
-    <mergeCell ref="G36:G95"/>
-    <mergeCell ref="A1:G2"/>
-    <mergeCell ref="A4:A20"/>
-    <mergeCell ref="A21:A35"/>
-    <mergeCell ref="A36:A95"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4995,7 +5046,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -5007,20 +5058,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A2" s="70"/>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" s="23" t="s">
@@ -5038,7 +5089,7 @@
       <c r="E3" s="23"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A4" s="65" t="s">
+      <c r="A4" s="69" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="23">
@@ -5048,12 +5099,12 @@
         <v>10</v>
       </c>
       <c r="D4" s="23"/>
-      <c r="E4" s="65" t="s">
+      <c r="E4" s="69" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A5" s="66"/>
+      <c r="A5" s="70"/>
       <c r="B5" s="23">
         <v>2</v>
       </c>
@@ -5063,10 +5114,10 @@
       <c r="D5" s="23" t="s">
         <v>181</v>
       </c>
-      <c r="E5" s="66"/>
+      <c r="E5" s="70"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A6" s="66"/>
+      <c r="A6" s="70"/>
       <c r="B6" s="23">
         <v>3</v>
       </c>
@@ -5074,10 +5125,10 @@
         <v>182</v>
       </c>
       <c r="D6" s="23"/>
-      <c r="E6" s="66"/>
+      <c r="E6" s="70"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A7" s="66"/>
+      <c r="A7" s="70"/>
       <c r="B7" s="23">
         <v>4</v>
       </c>
@@ -5085,10 +5136,10 @@
         <v>10</v>
       </c>
       <c r="D7" s="23"/>
-      <c r="E7" s="66"/>
+      <c r="E7" s="70"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A8" s="66"/>
+      <c r="A8" s="70"/>
       <c r="B8" s="23">
         <v>5</v>
       </c>
@@ -5096,10 +5147,10 @@
         <v>10</v>
       </c>
       <c r="D8" s="23"/>
-      <c r="E8" s="66"/>
+      <c r="E8" s="70"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A9" s="66"/>
+      <c r="A9" s="70"/>
       <c r="B9" s="23">
         <v>6</v>
       </c>
@@ -5107,10 +5158,10 @@
         <v>10</v>
       </c>
       <c r="D9" s="23"/>
-      <c r="E9" s="66"/>
+      <c r="E9" s="70"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A10" s="66"/>
+      <c r="A10" s="70"/>
       <c r="B10" s="23">
         <v>7</v>
       </c>
@@ -5118,10 +5169,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="23"/>
-      <c r="E10" s="66"/>
+      <c r="E10" s="70"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="66"/>
+      <c r="A11" s="70"/>
       <c r="B11" s="23">
         <v>8</v>
       </c>
@@ -5131,10 +5182,10 @@
       <c r="D11" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="E11" s="66"/>
+      <c r="E11" s="70"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A12" s="66"/>
+      <c r="A12" s="70"/>
       <c r="B12" s="23">
         <v>9</v>
       </c>
@@ -5142,13 +5193,13 @@
         <v>185</v>
       </c>
       <c r="D12" s="28"/>
-      <c r="E12" s="66"/>
+      <c r="E12" s="70"/>
       <c r="F12" s="8" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A13" s="66"/>
+      <c r="A13" s="70"/>
       <c r="B13" s="23">
         <v>10</v>
       </c>
@@ -5156,13 +5207,13 @@
         <v>187</v>
       </c>
       <c r="D13" s="28"/>
-      <c r="E13" s="66"/>
+      <c r="E13" s="70"/>
       <c r="F13" s="8" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A14" s="66"/>
+      <c r="A14" s="70"/>
       <c r="B14" s="23">
         <v>11</v>
       </c>
@@ -5170,13 +5221,13 @@
         <v>189</v>
       </c>
       <c r="D14" s="28"/>
-      <c r="E14" s="66"/>
+      <c r="E14" s="70"/>
       <c r="F14" s="8" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A15" s="66"/>
+      <c r="A15" s="70"/>
       <c r="B15" s="23">
         <v>12</v>
       </c>
@@ -5184,13 +5235,13 @@
         <v>191</v>
       </c>
       <c r="D15" s="28"/>
-      <c r="E15" s="66"/>
+      <c r="E15" s="70"/>
       <c r="F15" s="8" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A16" s="66"/>
+      <c r="A16" s="70"/>
       <c r="B16" s="23">
         <v>13</v>
       </c>
@@ -5198,13 +5249,13 @@
         <v>193</v>
       </c>
       <c r="D16" s="28"/>
-      <c r="E16" s="66"/>
+      <c r="E16" s="70"/>
       <c r="F16" s="8" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17" s="66"/>
+      <c r="A17" s="70"/>
       <c r="B17" s="23">
         <v>14</v>
       </c>
@@ -5212,13 +5263,13 @@
         <v>195</v>
       </c>
       <c r="D17" s="28"/>
-      <c r="E17" s="66"/>
+      <c r="E17" s="70"/>
       <c r="F17" s="8" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A18" s="66"/>
+      <c r="A18" s="70"/>
       <c r="B18" s="23">
         <v>15</v>
       </c>
@@ -5226,13 +5277,13 @@
         <v>197</v>
       </c>
       <c r="D18" s="28"/>
-      <c r="E18" s="66"/>
+      <c r="E18" s="70"/>
       <c r="F18" s="8" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A19" s="66"/>
+      <c r="A19" s="70"/>
       <c r="B19" s="23">
         <v>16</v>
       </c>
@@ -5240,13 +5291,13 @@
         <v>199</v>
       </c>
       <c r="D19" s="28"/>
-      <c r="E19" s="66"/>
+      <c r="E19" s="70"/>
       <c r="F19" s="8" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A20" s="66"/>
+      <c r="A20" s="70"/>
       <c r="B20" s="23">
         <v>17</v>
       </c>
@@ -5254,13 +5305,13 @@
         <v>201</v>
       </c>
       <c r="D20" s="28"/>
-      <c r="E20" s="66"/>
+      <c r="E20" s="70"/>
       <c r="F20" s="8" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A21" s="67"/>
+      <c r="A21" s="71"/>
       <c r="B21" s="23">
         <v>18</v>
       </c>
@@ -5268,10 +5319,10 @@
         <v>10</v>
       </c>
       <c r="D21" s="23"/>
-      <c r="E21" s="67"/>
+      <c r="E21" s="71"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A22" s="65" t="s">
+      <c r="A22" s="69" t="s">
         <v>20</v>
       </c>
       <c r="B22" s="23">
@@ -5280,10 +5331,10 @@
       <c r="C22" s="27" t="s">
         <v>203</v>
       </c>
-      <c r="D22" s="65" t="s">
+      <c r="D22" s="69" t="s">
         <v>204</v>
       </c>
-      <c r="E22" s="68" t="s">
+      <c r="E22" s="73" t="s">
         <v>21</v>
       </c>
       <c r="F22" s="8" t="s">
@@ -5291,7 +5342,7 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A23" s="66"/>
+      <c r="A23" s="70"/>
       <c r="B23" s="23">
         <f>B22+1</f>
         <v>101</v>
@@ -5299,14 +5350,14 @@
       <c r="C23" s="27" t="s">
         <v>206</v>
       </c>
-      <c r="D23" s="66"/>
-      <c r="E23" s="68"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="73"/>
       <c r="F23" s="8" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A24" s="66"/>
+      <c r="A24" s="70"/>
       <c r="B24" s="23">
         <f t="shared" ref="B24:B32" si="0">B23+1</f>
         <v>102</v>
@@ -5314,14 +5365,14 @@
       <c r="C24" s="29" t="s">
         <v>208</v>
       </c>
-      <c r="D24" s="66"/>
-      <c r="E24" s="68"/>
+      <c r="D24" s="70"/>
+      <c r="E24" s="73"/>
       <c r="F24" s="21" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A25" s="66"/>
+      <c r="A25" s="70"/>
       <c r="B25" s="23">
         <f t="shared" si="0"/>
         <v>103</v>
@@ -5329,14 +5380,14 @@
       <c r="C25" s="29" t="s">
         <v>210</v>
       </c>
-      <c r="D25" s="66"/>
-      <c r="E25" s="68"/>
+      <c r="D25" s="70"/>
+      <c r="E25" s="73"/>
       <c r="F25" s="21" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A26" s="66"/>
+      <c r="A26" s="70"/>
       <c r="B26" s="23">
         <f t="shared" si="0"/>
         <v>104</v>
@@ -5344,11 +5395,11 @@
       <c r="C26" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D26" s="67"/>
-      <c r="E26" s="68"/>
+      <c r="D26" s="71"/>
+      <c r="E26" s="73"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A27" s="66"/>
+      <c r="A27" s="70"/>
       <c r="B27" s="23">
         <f t="shared" si="0"/>
         <v>105</v>
@@ -5357,10 +5408,10 @@
         <v>8</v>
       </c>
       <c r="D27" s="24"/>
-      <c r="E27" s="68"/>
+      <c r="E27" s="73"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A28" s="66"/>
+      <c r="A28" s="70"/>
       <c r="B28" s="23">
         <f t="shared" si="0"/>
         <v>106</v>
@@ -5369,10 +5420,10 @@
         <v>8</v>
       </c>
       <c r="D28" s="25"/>
-      <c r="E28" s="68"/>
+      <c r="E28" s="73"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A29" s="66"/>
+      <c r="A29" s="70"/>
       <c r="B29" s="23">
         <f t="shared" si="0"/>
         <v>107</v>
@@ -5381,13 +5432,13 @@
         <v>212</v>
       </c>
       <c r="D29" s="23"/>
-      <c r="E29" s="68"/>
+      <c r="E29" s="73"/>
       <c r="F29" s="8" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A30" s="66"/>
+      <c r="A30" s="70"/>
       <c r="B30" s="23">
         <f t="shared" si="0"/>
         <v>108</v>
@@ -5398,13 +5449,13 @@
       <c r="D30" s="29" t="s">
         <v>215</v>
       </c>
-      <c r="E30" s="68"/>
+      <c r="E30" s="73"/>
       <c r="F30" s="21" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="66"/>
+      <c r="A31" s="70"/>
       <c r="B31" s="23">
         <f t="shared" si="0"/>
         <v>109</v>
@@ -5413,13 +5464,13 @@
         <v>217</v>
       </c>
       <c r="D31" s="29"/>
-      <c r="E31" s="68"/>
+      <c r="E31" s="73"/>
       <c r="F31" s="21" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="66"/>
+      <c r="A32" s="70"/>
       <c r="B32" s="23">
         <f t="shared" si="0"/>
         <v>110</v>
@@ -5428,13 +5479,13 @@
         <v>219</v>
       </c>
       <c r="D32" s="23"/>
-      <c r="E32" s="68"/>
+      <c r="E32" s="73"/>
       <c r="F32" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A33" s="66"/>
+      <c r="A33" s="70"/>
       <c r="B33" s="23">
         <v>111</v>
       </c>
@@ -5442,13 +5493,13 @@
         <v>220</v>
       </c>
       <c r="D33" s="28"/>
-      <c r="E33" s="68"/>
+      <c r="E33" s="73"/>
       <c r="F33" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A34" s="66"/>
+      <c r="A34" s="70"/>
       <c r="B34" s="23">
         <v>112</v>
       </c>
@@ -5458,13 +5509,13 @@
       <c r="D34" s="28" t="s">
         <v>222</v>
       </c>
-      <c r="E34" s="68"/>
+      <c r="E34" s="73"/>
       <c r="F34" s="8" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A35" s="66"/>
+      <c r="A35" s="70"/>
       <c r="B35" s="23">
         <v>113</v>
       </c>
@@ -5474,27 +5525,27 @@
       <c r="D35" s="28" t="s">
         <v>225</v>
       </c>
-      <c r="E35" s="68"/>
+      <c r="E35" s="73"/>
       <c r="F35" s="8" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A36" s="66"/>
+      <c r="A36" s="70"/>
       <c r="B36" s="23">
         <v>114</v>
       </c>
-      <c r="C36" s="27" t="s">
-        <v>227</v>
+      <c r="C36" s="54" t="s">
+        <v>459</v>
       </c>
       <c r="D36" s="28"/>
-      <c r="E36" s="68"/>
+      <c r="E36" s="73"/>
       <c r="F36" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A37" s="66"/>
+      <c r="A37" s="70"/>
       <c r="B37" s="23">
         <v>115</v>
       </c>
@@ -5504,13 +5555,13 @@
       <c r="D37" s="28" t="s">
         <v>229</v>
       </c>
-      <c r="E37" s="68"/>
+      <c r="E37" s="73"/>
       <c r="F37" s="8" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A38" s="66"/>
+      <c r="A38" s="70"/>
       <c r="B38" s="23">
         <v>116</v>
       </c>
@@ -5520,13 +5571,13 @@
       <c r="D38" s="28" t="s">
         <v>232</v>
       </c>
-      <c r="E38" s="68"/>
+      <c r="E38" s="73"/>
       <c r="F38" s="8" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A39" s="66"/>
+      <c r="A39" s="70"/>
       <c r="B39" s="23">
         <v>117</v>
       </c>
@@ -5534,13 +5585,13 @@
         <v>234</v>
       </c>
       <c r="D39" s="28"/>
-      <c r="E39" s="68"/>
+      <c r="E39" s="73"/>
       <c r="F39" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A40" s="66"/>
+      <c r="A40" s="70"/>
       <c r="B40" s="23">
         <v>118</v>
       </c>
@@ -5550,13 +5601,13 @@
       <c r="D40" s="28" t="s">
         <v>236</v>
       </c>
-      <c r="E40" s="68"/>
+      <c r="E40" s="73"/>
       <c r="F40" s="8" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A41" s="66"/>
+      <c r="A41" s="70"/>
       <c r="B41" s="23">
         <v>119</v>
       </c>
@@ -5564,13 +5615,13 @@
         <v>238</v>
       </c>
       <c r="D41" s="28"/>
-      <c r="E41" s="68"/>
+      <c r="E41" s="73"/>
       <c r="F41" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A42" s="66"/>
+      <c r="A42" s="70"/>
       <c r="B42" s="23">
         <v>120</v>
       </c>
@@ -5580,13 +5631,13 @@
       <c r="D42" s="28" t="s">
         <v>240</v>
       </c>
-      <c r="E42" s="68"/>
+      <c r="E42" s="73"/>
       <c r="F42" s="8" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A43" s="66"/>
+      <c r="A43" s="70"/>
       <c r="B43" s="23">
         <v>121</v>
       </c>
@@ -5594,13 +5645,13 @@
         <v>242</v>
       </c>
       <c r="D43" s="28"/>
-      <c r="E43" s="68"/>
+      <c r="E43" s="73"/>
       <c r="F43" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A44" s="66"/>
+      <c r="A44" s="70"/>
       <c r="B44" s="23">
         <v>122</v>
       </c>
@@ -5610,13 +5661,13 @@
       <c r="D44" s="28" t="s">
         <v>244</v>
       </c>
-      <c r="E44" s="68"/>
+      <c r="E44" s="73"/>
       <c r="F44" s="8" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A45" s="66"/>
+      <c r="A45" s="70"/>
       <c r="B45" s="23">
         <v>123</v>
       </c>
@@ -5624,13 +5675,13 @@
         <v>246</v>
       </c>
       <c r="D45" s="28"/>
-      <c r="E45" s="68"/>
+      <c r="E45" s="73"/>
       <c r="F45" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A46" s="66"/>
+      <c r="A46" s="70"/>
       <c r="B46" s="23">
         <v>124</v>
       </c>
@@ -5640,13 +5691,13 @@
       <c r="D46" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="E46" s="68"/>
+      <c r="E46" s="73"/>
       <c r="F46" s="8" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A47" s="66"/>
+      <c r="A47" s="70"/>
       <c r="B47" s="23">
         <v>125</v>
       </c>
@@ -5654,13 +5705,13 @@
         <v>250</v>
       </c>
       <c r="D47" s="28"/>
-      <c r="E47" s="68"/>
+      <c r="E47" s="73"/>
       <c r="F47" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A48" s="66"/>
+      <c r="A48" s="70"/>
       <c r="B48" s="23">
         <v>126</v>
       </c>
@@ -5670,13 +5721,13 @@
       <c r="D48" s="28" t="s">
         <v>252</v>
       </c>
-      <c r="E48" s="68"/>
+      <c r="E48" s="73"/>
       <c r="F48" s="8" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A49" s="66"/>
+      <c r="A49" s="70"/>
       <c r="B49" s="23">
         <v>127</v>
       </c>
@@ -5686,13 +5737,13 @@
       <c r="D49" s="28" t="s">
         <v>255</v>
       </c>
-      <c r="E49" s="68"/>
+      <c r="E49" s="73"/>
       <c r="F49" s="8" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="66"/>
+      <c r="A50" s="70"/>
       <c r="B50" s="23">
         <v>128</v>
       </c>
@@ -5702,13 +5753,13 @@
       <c r="D50" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="E50" s="68"/>
+      <c r="E50" s="73"/>
       <c r="F50" s="8" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A51" s="66"/>
+      <c r="A51" s="70"/>
       <c r="B51" s="23">
         <v>129</v>
       </c>
@@ -5716,13 +5767,13 @@
         <v>259</v>
       </c>
       <c r="D51" s="32"/>
-      <c r="E51" s="68"/>
+      <c r="E51" s="73"/>
       <c r="F51" s="8" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A52" s="66"/>
+      <c r="A52" s="70"/>
       <c r="B52" s="23">
         <v>130</v>
       </c>
@@ -5730,13 +5781,13 @@
         <v>261</v>
       </c>
       <c r="D52" s="32"/>
-      <c r="E52" s="68"/>
+      <c r="E52" s="73"/>
       <c r="F52" s="8" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A53" s="66"/>
+      <c r="A53" s="70"/>
       <c r="B53" s="23">
         <v>131</v>
       </c>
@@ -5746,13 +5797,13 @@
       <c r="D53" s="32" t="s">
         <v>264</v>
       </c>
-      <c r="E53" s="68"/>
+      <c r="E53" s="73"/>
       <c r="F53" s="8" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A54" s="66"/>
+      <c r="A54" s="70"/>
       <c r="B54" s="23">
         <v>132</v>
       </c>
@@ -5762,13 +5813,13 @@
       <c r="D54" s="34" t="s">
         <v>267</v>
       </c>
-      <c r="E54" s="68"/>
+      <c r="E54" s="73"/>
       <c r="F54" s="8" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="27.75" x14ac:dyDescent="0.4">
-      <c r="A55" s="66"/>
+      <c r="A55" s="70"/>
       <c r="B55" s="23">
         <v>133</v>
       </c>
@@ -5778,13 +5829,13 @@
       <c r="D55" s="34" t="s">
         <v>270</v>
       </c>
-      <c r="E55" s="68"/>
+      <c r="E55" s="73"/>
       <c r="F55" s="8" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A56" s="66"/>
+      <c r="A56" s="70"/>
       <c r="B56" s="23">
         <v>134</v>
       </c>
@@ -5794,13 +5845,13 @@
       <c r="D56" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="E56" s="68"/>
+      <c r="E56" s="73"/>
       <c r="F56" s="8" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A57" s="66"/>
+      <c r="A57" s="70"/>
       <c r="B57" s="23">
         <v>135</v>
       </c>
@@ -5810,83 +5861,83 @@
       <c r="D57" s="72" t="s">
         <v>276</v>
       </c>
-      <c r="E57" s="68"/>
+      <c r="E57" s="73"/>
       <c r="F57" s="8" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A58" s="66"/>
+      <c r="A58" s="70"/>
       <c r="B58" s="23">
         <v>136</v>
       </c>
       <c r="C58" s="27" t="s">
         <v>278</v>
       </c>
-      <c r="D58" s="68"/>
-      <c r="E58" s="68"/>
+      <c r="D58" s="73"/>
+      <c r="E58" s="73"/>
       <c r="F58" s="8" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A59" s="66"/>
+      <c r="A59" s="70"/>
       <c r="B59" s="23">
         <v>137</v>
       </c>
       <c r="C59" s="27" t="s">
         <v>280</v>
       </c>
-      <c r="D59" s="68"/>
-      <c r="E59" s="68"/>
+      <c r="D59" s="73"/>
+      <c r="E59" s="73"/>
       <c r="F59" s="8" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A60" s="66"/>
+      <c r="A60" s="70"/>
       <c r="B60" s="23">
         <v>138</v>
       </c>
       <c r="C60" s="27" t="s">
         <v>282</v>
       </c>
-      <c r="D60" s="68"/>
-      <c r="E60" s="68"/>
+      <c r="D60" s="73"/>
+      <c r="E60" s="73"/>
       <c r="F60" s="8" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A61" s="66"/>
+      <c r="A61" s="70"/>
       <c r="B61" s="23">
         <v>139</v>
       </c>
       <c r="C61" s="27" t="s">
         <v>284</v>
       </c>
-      <c r="D61" s="68"/>
-      <c r="E61" s="68"/>
+      <c r="D61" s="73"/>
+      <c r="E61" s="73"/>
       <c r="F61" s="8" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A62" s="66"/>
+      <c r="A62" s="70"/>
       <c r="B62" s="23">
         <v>140</v>
       </c>
       <c r="C62" s="27" t="s">
         <v>286</v>
       </c>
-      <c r="D62" s="69"/>
-      <c r="E62" s="68"/>
+      <c r="D62" s="74"/>
+      <c r="E62" s="73"/>
       <c r="F62" s="8" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A63" s="66"/>
+      <c r="A63" s="70"/>
       <c r="B63" s="23">
         <v>141</v>
       </c>
@@ -5896,41 +5947,41 @@
       <c r="D63" s="72" t="s">
         <v>289</v>
       </c>
-      <c r="E63" s="68"/>
+      <c r="E63" s="73"/>
       <c r="F63" s="8" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A64" s="66"/>
+      <c r="A64" s="70"/>
       <c r="B64" s="23">
         <v>142</v>
       </c>
       <c r="C64" s="27" t="s">
         <v>291</v>
       </c>
-      <c r="D64" s="68"/>
-      <c r="E64" s="68"/>
+      <c r="D64" s="73"/>
+      <c r="E64" s="73"/>
       <c r="F64" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A65" s="66"/>
+      <c r="A65" s="70"/>
       <c r="B65" s="23">
         <v>143</v>
       </c>
       <c r="C65" s="27" t="s">
         <v>292</v>
       </c>
-      <c r="D65" s="69"/>
-      <c r="E65" s="68"/>
+      <c r="D65" s="74"/>
+      <c r="E65" s="73"/>
       <c r="F65" s="8" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A66" s="66"/>
+      <c r="A66" s="70"/>
       <c r="B66" s="23">
         <v>144</v>
       </c>
@@ -5940,13 +5991,13 @@
       <c r="D66" s="32" t="s">
         <v>295</v>
       </c>
-      <c r="E66" s="68"/>
+      <c r="E66" s="73"/>
       <c r="F66" s="8" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="27.75" x14ac:dyDescent="0.4">
-      <c r="A67" s="66"/>
+      <c r="A67" s="70"/>
       <c r="B67" s="23">
         <v>145</v>
       </c>
@@ -5956,13 +6007,13 @@
       <c r="D67" s="32" t="s">
         <v>298</v>
       </c>
-      <c r="E67" s="68"/>
+      <c r="E67" s="73"/>
       <c r="F67" s="8" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="27.75" x14ac:dyDescent="0.4">
-      <c r="A68" s="66"/>
+      <c r="A68" s="70"/>
       <c r="B68" s="23">
         <v>146</v>
       </c>
@@ -5972,13 +6023,13 @@
       <c r="D68" s="32" t="s">
         <v>301</v>
       </c>
-      <c r="E68" s="68"/>
+      <c r="E68" s="73"/>
       <c r="F68" s="8" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="27.75" x14ac:dyDescent="0.4">
-      <c r="A69" s="66"/>
+      <c r="A69" s="70"/>
       <c r="B69" s="23">
         <v>147</v>
       </c>
@@ -5986,13 +6037,13 @@
         <v>303</v>
       </c>
       <c r="D69" s="34"/>
-      <c r="E69" s="68"/>
+      <c r="E69" s="73"/>
       <c r="F69" s="8" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A70" s="66"/>
+      <c r="A70" s="70"/>
       <c r="B70" s="23">
         <v>148</v>
       </c>
@@ -6000,13 +6051,13 @@
         <v>305</v>
       </c>
       <c r="D70" s="34"/>
-      <c r="E70" s="68"/>
+      <c r="E70" s="73"/>
       <c r="F70" s="8" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A71" s="66"/>
+      <c r="A71" s="70"/>
       <c r="B71" s="23">
         <v>149</v>
       </c>
@@ -6016,41 +6067,41 @@
       <c r="D71" s="72" t="s">
         <v>308</v>
       </c>
-      <c r="E71" s="68"/>
+      <c r="E71" s="73"/>
       <c r="F71" s="8" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A72" s="66"/>
+      <c r="A72" s="70"/>
       <c r="B72" s="23">
         <v>150</v>
       </c>
       <c r="C72" s="27" t="s">
         <v>310</v>
       </c>
-      <c r="D72" s="68"/>
-      <c r="E72" s="68"/>
+      <c r="D72" s="73"/>
+      <c r="E72" s="73"/>
       <c r="F72" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A73" s="66"/>
+      <c r="A73" s="70"/>
       <c r="B73" s="23">
         <v>151</v>
       </c>
       <c r="C73" s="27" t="s">
         <v>311</v>
       </c>
-      <c r="D73" s="69"/>
-      <c r="E73" s="68"/>
+      <c r="D73" s="74"/>
+      <c r="E73" s="73"/>
       <c r="F73" s="8" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A74" s="66"/>
+      <c r="A74" s="70"/>
       <c r="B74" s="23">
         <v>152</v>
       </c>
@@ -6058,13 +6109,13 @@
         <v>313</v>
       </c>
       <c r="D74" s="34"/>
-      <c r="E74" s="68"/>
+      <c r="E74" s="73"/>
       <c r="F74" s="8" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A75" s="66"/>
+      <c r="A75" s="70"/>
       <c r="B75" s="23">
         <v>153</v>
       </c>
@@ -6072,13 +6123,13 @@
         <v>315</v>
       </c>
       <c r="D75" s="34"/>
-      <c r="E75" s="68"/>
+      <c r="E75" s="73"/>
       <c r="F75" s="8" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A76" s="66"/>
+      <c r="A76" s="70"/>
       <c r="B76" s="23">
         <v>154</v>
       </c>
@@ -6086,49 +6137,49 @@
         <v>317</v>
       </c>
       <c r="D76" s="34"/>
-      <c r="E76" s="68"/>
+      <c r="E76" s="73"/>
       <c r="F76" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A77" s="66"/>
+      <c r="A77" s="70"/>
       <c r="B77" s="23">
         <v>155</v>
       </c>
       <c r="C77" s="23"/>
       <c r="D77" s="34"/>
-      <c r="E77" s="68"/>
+      <c r="E77" s="73"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A78" s="66"/>
+      <c r="A78" s="70"/>
       <c r="B78" s="23">
         <v>156</v>
       </c>
       <c r="C78" s="23"/>
       <c r="D78" s="34"/>
-      <c r="E78" s="68"/>
+      <c r="E78" s="73"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A79" s="66"/>
+      <c r="A79" s="70"/>
       <c r="B79" s="23">
         <v>157</v>
       </c>
       <c r="C79" s="23"/>
       <c r="D79" s="34"/>
-      <c r="E79" s="68"/>
+      <c r="E79" s="73"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A80" s="66"/>
+      <c r="A80" s="70"/>
       <c r="B80" s="23">
         <v>158</v>
       </c>
       <c r="C80" s="23"/>
       <c r="D80" s="34"/>
-      <c r="E80" s="68"/>
+      <c r="E80" s="73"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A81" s="66"/>
+      <c r="A81" s="70"/>
       <c r="B81" s="23">
         <v>159</v>
       </c>
@@ -6138,41 +6189,41 @@
       <c r="D81" s="72" t="s">
         <v>320</v>
       </c>
-      <c r="E81" s="68"/>
+      <c r="E81" s="73"/>
       <c r="F81" s="8" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A82" s="66"/>
+      <c r="A82" s="70"/>
       <c r="B82" s="23">
         <v>160</v>
       </c>
       <c r="C82" s="27" t="s">
         <v>322</v>
       </c>
-      <c r="D82" s="68"/>
-      <c r="E82" s="68"/>
+      <c r="D82" s="73"/>
+      <c r="E82" s="73"/>
       <c r="F82" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A83" s="66"/>
+      <c r="A83" s="70"/>
       <c r="B83" s="23">
         <v>161</v>
       </c>
       <c r="C83" s="27" t="s">
         <v>323</v>
       </c>
-      <c r="D83" s="69"/>
-      <c r="E83" s="68"/>
+      <c r="D83" s="74"/>
+      <c r="E83" s="73"/>
       <c r="F83" s="8" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A84" s="66"/>
+      <c r="A84" s="70"/>
       <c r="B84" s="23">
         <v>162</v>
       </c>
@@ -6180,20 +6231,20 @@
         <v>325</v>
       </c>
       <c r="D84" s="32"/>
-      <c r="E84" s="68"/>
+      <c r="E84" s="73"/>
       <c r="F84" s="8" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A85" s="66"/>
+      <c r="A85" s="70"/>
       <c r="B85" s="23"/>
       <c r="C85" s="27"/>
       <c r="D85" s="32"/>
-      <c r="E85" s="68"/>
+      <c r="E85" s="73"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A86" s="66"/>
+      <c r="A86" s="70"/>
       <c r="B86" s="23">
         <v>170</v>
       </c>
@@ -6201,10 +6252,10 @@
         <v>443</v>
       </c>
       <c r="D86" s="32"/>
-      <c r="E86" s="68"/>
+      <c r="E86" s="73"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A87" s="66"/>
+      <c r="A87" s="70"/>
       <c r="B87" s="23">
         <v>171</v>
       </c>
@@ -6212,10 +6263,10 @@
         <v>446</v>
       </c>
       <c r="D87" s="32"/>
-      <c r="E87" s="68"/>
+      <c r="E87" s="73"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A88" s="66"/>
+      <c r="A88" s="70"/>
       <c r="B88" s="8">
         <v>172</v>
       </c>
@@ -6223,10 +6274,10 @@
         <v>447</v>
       </c>
       <c r="D88" s="32"/>
-      <c r="E88" s="68"/>
+      <c r="E88" s="73"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A89" s="67"/>
+      <c r="A89" s="71"/>
       <c r="B89" s="8">
         <v>173</v>
       </c>
@@ -6234,105 +6285,130 @@
         <v>449</v>
       </c>
       <c r="D89" s="32"/>
-      <c r="E89" s="69"/>
+      <c r="E89" s="74"/>
     </row>
     <row r="90" spans="1:6" ht="55.5" x14ac:dyDescent="0.4">
-      <c r="B90" s="94">
+      <c r="B90" s="43">
         <v>180</v>
       </c>
-      <c r="C90" s="94">
+      <c r="C90" s="43">
         <v>180</v>
       </c>
-      <c r="D90" s="96" t="s">
+      <c r="D90" s="66" t="s">
         <v>457</v>
       </c>
-      <c r="E90" s="95" t="s">
+      <c r="E90" s="65" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A91" s="76" t="s">
+      <c r="B91" s="43">
+        <v>190</v>
+      </c>
+      <c r="C91" s="67" t="s">
+        <v>458</v>
+      </c>
+      <c r="D91" s="66"/>
+      <c r="E91" s="65"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B92" s="43">
+        <v>192</v>
+      </c>
+      <c r="C92" s="67" t="s">
+        <v>461</v>
+      </c>
+      <c r="D92" s="66"/>
+      <c r="E92" s="65"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A93" s="79" t="s">
         <v>327</v>
       </c>
-      <c r="B91" s="23">
+      <c r="B93" s="23">
         <v>50000</v>
       </c>
-      <c r="C91" s="27" t="s">
+      <c r="C93" s="27" t="s">
         <v>328</v>
       </c>
-      <c r="D91" s="23"/>
-      <c r="E91" s="3"/>
-      <c r="F91" s="8" t="s">
+      <c r="D93" s="23"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="8" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A92" s="76"/>
-      <c r="B92" s="2">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A94" s="79"/>
+      <c r="B94" s="2">
         <v>50001</v>
       </c>
-      <c r="C92" s="27" t="s">
+      <c r="C94" s="27" t="s">
         <v>208</v>
       </c>
-      <c r="D92" s="2"/>
-      <c r="E92" s="3"/>
-      <c r="F92" s="8" t="s">
+      <c r="D94" s="2"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="8" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A93" s="76"/>
-      <c r="B93" s="2">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A95" s="79"/>
+      <c r="B95" s="2">
         <v>50002</v>
       </c>
-      <c r="C93" s="27" t="s">
+      <c r="C95" s="27" t="s">
         <v>210</v>
       </c>
-      <c r="D93" s="2"/>
-      <c r="E93" s="38"/>
-      <c r="F93" s="8" t="s">
+      <c r="D95" s="2"/>
+      <c r="E95" s="38"/>
+      <c r="F95" s="8" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A94" s="76"/>
-      <c r="B94" s="2">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A96" s="79"/>
+      <c r="B96" s="2">
         <v>50003</v>
       </c>
-      <c r="C94" s="13"/>
-      <c r="D94" s="13"/>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="C95" s="39"/>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="C96" s="39"/>
-      <c r="E96" s="40"/>
-    </row>
-    <row r="97" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B97" s="39"/>
-      <c r="C97" s="39"/>
-      <c r="D97" s="39"/>
-    </row>
-    <row r="98" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C96" s="13"/>
+      <c r="D96" s="13"/>
+    </row>
+    <row r="97" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B97" s="8">
+        <v>50010</v>
+      </c>
+      <c r="C97" s="39" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="98" spans="2:5" x14ac:dyDescent="0.4">
       <c r="C98" s="39"/>
-    </row>
-    <row r="99" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="E98" s="40"/>
+    </row>
+    <row r="99" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B99" s="39"/>
       <c r="C99" s="39"/>
+      <c r="D99" s="39"/>
+    </row>
+    <row r="100" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="C100" s="39"/>
+    </row>
+    <row r="101" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="C101" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A91:A94"/>
+    <mergeCell ref="E4:E21"/>
+    <mergeCell ref="E22:E89"/>
+    <mergeCell ref="A1:E2"/>
+    <mergeCell ref="A4:A21"/>
+    <mergeCell ref="A22:A89"/>
+    <mergeCell ref="A93:A96"/>
     <mergeCell ref="D22:D26"/>
     <mergeCell ref="D57:D62"/>
     <mergeCell ref="D63:D65"/>
     <mergeCell ref="D71:D73"/>
     <mergeCell ref="D81:D83"/>
-    <mergeCell ref="E4:E21"/>
-    <mergeCell ref="E22:E89"/>
-    <mergeCell ref="A1:E2"/>
-    <mergeCell ref="A4:A21"/>
-    <mergeCell ref="A22:A89"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6368,26 +6444,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="409.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="80" t="s">
         <v>330</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="86"/>
-      <c r="F1" s="86"/>
-      <c r="G1" s="86"/>
-      <c r="H1" s="86"/>
-      <c r="I1" s="86"/>
-      <c r="J1" s="86"/>
-      <c r="K1" s="86"/>
-      <c r="L1" s="86"/>
-      <c r="M1" s="86"/>
-      <c r="N1" s="86"/>
-      <c r="O1" s="86"/>
-      <c r="P1" s="86"/>
-      <c r="Q1" s="86"/>
-      <c r="R1" s="86"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
+      <c r="M1" s="80"/>
+      <c r="N1" s="80"/>
+      <c r="O1" s="80"/>
+      <c r="P1" s="80"/>
+      <c r="Q1" s="80"/>
+      <c r="R1" s="80"/>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A2" s="9"/>
@@ -6406,32 +6482,32 @@
       <c r="N2" s="9"/>
     </row>
     <row r="3" spans="1:24" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="87" t="s">
+      <c r="A3" s="81" t="s">
         <v>331</v>
       </c>
-      <c r="B3" s="87"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="87"/>
-      <c r="H3" s="87"/>
-      <c r="I3" s="87"/>
-      <c r="J3" s="87"/>
-      <c r="K3" s="87"/>
-      <c r="L3" s="87"/>
-      <c r="M3" s="87"/>
-      <c r="N3" s="87"/>
-      <c r="O3" s="87"/>
-      <c r="P3" s="87"/>
-      <c r="Q3" s="87"/>
-      <c r="R3" s="87"/>
-      <c r="S3" s="87"/>
-      <c r="T3" s="87"/>
-      <c r="U3" s="87"/>
-      <c r="V3" s="87"/>
-      <c r="W3" s="87"/>
-      <c r="X3" s="87"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="81"/>
+      <c r="K3" s="81"/>
+      <c r="L3" s="81"/>
+      <c r="M3" s="81"/>
+      <c r="N3" s="81"/>
+      <c r="O3" s="81"/>
+      <c r="P3" s="81"/>
+      <c r="Q3" s="81"/>
+      <c r="R3" s="81"/>
+      <c r="S3" s="81"/>
+      <c r="T3" s="81"/>
+      <c r="U3" s="81"/>
+      <c r="V3" s="81"/>
+      <c r="W3" s="81"/>
+      <c r="X3" s="81"/>
     </row>
     <row r="4" spans="1:24" s="6" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A4" s="10" t="s">
@@ -6552,73 +6628,73 @@
       </c>
     </row>
     <row r="6" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="88"/>
-      <c r="B6" s="88"/>
-      <c r="C6" s="88"/>
-      <c r="D6" s="88"/>
-      <c r="E6" s="88"/>
-      <c r="F6" s="88"/>
-      <c r="G6" s="88"/>
-      <c r="H6" s="88"/>
-      <c r="I6" s="88"/>
-      <c r="J6" s="88"/>
-      <c r="K6" s="88"/>
-      <c r="L6" s="88"/>
-      <c r="M6" s="88"/>
-      <c r="N6" s="88"/>
-      <c r="O6" s="88"/>
-      <c r="P6" s="88"/>
-      <c r="Q6" s="88"/>
-      <c r="R6" s="88"/>
+      <c r="A6" s="82"/>
+      <c r="B6" s="82"/>
+      <c r="C6" s="82"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="82"/>
+      <c r="G6" s="82"/>
+      <c r="H6" s="82"/>
+      <c r="I6" s="82"/>
+      <c r="J6" s="82"/>
+      <c r="K6" s="82"/>
+      <c r="L6" s="82"/>
+      <c r="M6" s="82"/>
+      <c r="N6" s="82"/>
+      <c r="O6" s="82"/>
+      <c r="P6" s="82"/>
+      <c r="Q6" s="82"/>
+      <c r="R6" s="82"/>
     </row>
     <row r="7" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="88"/>
-      <c r="B7" s="88"/>
-      <c r="C7" s="88"/>
-      <c r="D7" s="88"/>
-      <c r="E7" s="88"/>
-      <c r="F7" s="88"/>
-      <c r="G7" s="88"/>
-      <c r="H7" s="88"/>
-      <c r="I7" s="88"/>
-      <c r="J7" s="88"/>
-      <c r="K7" s="88"/>
-      <c r="L7" s="88"/>
-      <c r="M7" s="88"/>
-      <c r="N7" s="88"/>
-      <c r="O7" s="88"/>
-      <c r="P7" s="88"/>
-      <c r="Q7" s="88"/>
-      <c r="R7" s="88"/>
+      <c r="A7" s="82"/>
+      <c r="B7" s="82"/>
+      <c r="C7" s="82"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="82"/>
+      <c r="H7" s="82"/>
+      <c r="I7" s="82"/>
+      <c r="J7" s="82"/>
+      <c r="K7" s="82"/>
+      <c r="L7" s="82"/>
+      <c r="M7" s="82"/>
+      <c r="N7" s="82"/>
+      <c r="O7" s="82"/>
+      <c r="P7" s="82"/>
+      <c r="Q7" s="82"/>
+      <c r="R7" s="82"/>
     </row>
     <row r="8" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.4"/>
     <row r="9" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="84" t="s">
+      <c r="A9" s="83" t="s">
         <v>350</v>
       </c>
-      <c r="B9" s="84"/>
-      <c r="C9" s="84"/>
-      <c r="D9" s="84"/>
-      <c r="E9" s="84"/>
-      <c r="F9" s="84"/>
-      <c r="G9" s="84"/>
-      <c r="H9" s="84"/>
-      <c r="I9" s="84"/>
-      <c r="J9" s="84"/>
-      <c r="K9" s="84"/>
-      <c r="L9" s="84"/>
-      <c r="M9" s="84"/>
-      <c r="N9" s="84"/>
-      <c r="O9" s="84"/>
-      <c r="P9" s="84"/>
-      <c r="Q9" s="84"/>
-      <c r="R9" s="84"/>
-      <c r="S9" s="84"/>
-      <c r="T9" s="84"/>
-      <c r="U9" s="84"/>
-      <c r="V9" s="84"/>
-      <c r="W9" s="84"/>
-      <c r="X9" s="84"/>
+      <c r="B9" s="83"/>
+      <c r="C9" s="83"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
+      <c r="I9" s="83"/>
+      <c r="J9" s="83"/>
+      <c r="K9" s="83"/>
+      <c r="L9" s="83"/>
+      <c r="M9" s="83"/>
+      <c r="N9" s="83"/>
+      <c r="O9" s="83"/>
+      <c r="P9" s="83"/>
+      <c r="Q9" s="83"/>
+      <c r="R9" s="83"/>
+      <c r="S9" s="83"/>
+      <c r="T9" s="83"/>
+      <c r="U9" s="83"/>
+      <c r="V9" s="83"/>
+      <c r="W9" s="83"/>
+      <c r="X9" s="83"/>
     </row>
     <row r="10" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A10" s="12" t="s">
@@ -6694,14 +6770,14 @@
       <c r="X11" s="14"/>
     </row>
     <row r="12" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="81" t="s">
+      <c r="A12" s="84" t="s">
         <v>351</v>
       </c>
-      <c r="B12" s="82"/>
-      <c r="C12" s="82"/>
-      <c r="D12" s="82"/>
-      <c r="E12" s="82"/>
-      <c r="F12" s="83"/>
+      <c r="B12" s="85"/>
+      <c r="C12" s="85"/>
+      <c r="D12" s="85"/>
+      <c r="E12" s="85"/>
+      <c r="F12" s="86"/>
       <c r="G12" s="14"/>
       <c r="H12" s="14"/>
       <c r="I12" s="14"/>
@@ -6831,26 +6907,26 @@
       <c r="X14" s="14"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.4">
-      <c r="A15" s="84" t="s">
+      <c r="A15" s="83" t="s">
         <v>355</v>
       </c>
-      <c r="B15" s="84"/>
-      <c r="C15" s="84"/>
-      <c r="D15" s="84"/>
-      <c r="E15" s="84"/>
-      <c r="F15" s="84"/>
-      <c r="G15" s="84"/>
-      <c r="H15" s="84"/>
-      <c r="I15" s="84"/>
-      <c r="J15" s="84"/>
-      <c r="K15" s="84"/>
-      <c r="L15" s="84"/>
-      <c r="M15" s="84"/>
-      <c r="N15" s="84"/>
-      <c r="O15" s="84"/>
-      <c r="P15" s="85"/>
-      <c r="Q15" s="84"/>
-      <c r="R15" s="84"/>
+      <c r="B15" s="83"/>
+      <c r="C15" s="83"/>
+      <c r="D15" s="83"/>
+      <c r="E15" s="83"/>
+      <c r="F15" s="83"/>
+      <c r="G15" s="83"/>
+      <c r="H15" s="83"/>
+      <c r="I15" s="83"/>
+      <c r="J15" s="83"/>
+      <c r="K15" s="83"/>
+      <c r="L15" s="83"/>
+      <c r="M15" s="83"/>
+      <c r="N15" s="83"/>
+      <c r="O15" s="83"/>
+      <c r="P15" s="87"/>
+      <c r="Q15" s="83"/>
+      <c r="R15" s="83"/>
       <c r="S15" s="21"/>
       <c r="T15" s="21"/>
       <c r="U15" s="21"/>
@@ -6859,24 +6935,24 @@
       <c r="X15" s="21"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.4">
-      <c r="A16" s="84"/>
-      <c r="B16" s="84"/>
-      <c r="C16" s="84"/>
-      <c r="D16" s="84"/>
-      <c r="E16" s="84"/>
-      <c r="F16" s="84"/>
-      <c r="G16" s="84"/>
-      <c r="H16" s="84"/>
-      <c r="I16" s="84"/>
-      <c r="J16" s="84"/>
-      <c r="K16" s="84"/>
-      <c r="L16" s="84"/>
-      <c r="M16" s="84"/>
-      <c r="N16" s="84"/>
-      <c r="O16" s="84"/>
-      <c r="P16" s="84"/>
-      <c r="Q16" s="84"/>
-      <c r="R16" s="84"/>
+      <c r="A16" s="83"/>
+      <c r="B16" s="83"/>
+      <c r="C16" s="83"/>
+      <c r="D16" s="83"/>
+      <c r="E16" s="83"/>
+      <c r="F16" s="83"/>
+      <c r="G16" s="83"/>
+      <c r="H16" s="83"/>
+      <c r="I16" s="83"/>
+      <c r="J16" s="83"/>
+      <c r="K16" s="83"/>
+      <c r="L16" s="83"/>
+      <c r="M16" s="83"/>
+      <c r="N16" s="83"/>
+      <c r="O16" s="83"/>
+      <c r="P16" s="83"/>
+      <c r="Q16" s="83"/>
+      <c r="R16" s="83"/>
       <c r="S16" s="21"/>
       <c r="T16" s="21"/>
       <c r="U16" s="21"/>
@@ -6887,32 +6963,32 @@
     <row r="17" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.4"/>
     <row r="19" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="79" t="s">
+      <c r="A19" s="88" t="s">
         <v>356</v>
       </c>
-      <c r="B19" s="77"/>
-      <c r="C19" s="77"/>
-      <c r="D19" s="77"/>
-      <c r="E19" s="77"/>
-      <c r="F19" s="77"/>
-      <c r="G19" s="77"/>
-      <c r="H19" s="77"/>
-      <c r="I19" s="77"/>
-      <c r="J19" s="77"/>
-      <c r="K19" s="77"/>
-      <c r="L19" s="77"/>
-      <c r="M19" s="77"/>
-      <c r="N19" s="77"/>
-      <c r="O19" s="77"/>
-      <c r="P19" s="77"/>
-      <c r="Q19" s="77"/>
-      <c r="R19" s="77"/>
-      <c r="S19" s="77"/>
-      <c r="T19" s="77"/>
-      <c r="U19" s="77"/>
-      <c r="V19" s="77"/>
-      <c r="W19" s="77"/>
-      <c r="X19" s="77"/>
+      <c r="B19" s="89"/>
+      <c r="C19" s="89"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="89"/>
+      <c r="G19" s="89"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="89"/>
+      <c r="J19" s="89"/>
+      <c r="K19" s="89"/>
+      <c r="L19" s="89"/>
+      <c r="M19" s="89"/>
+      <c r="N19" s="89"/>
+      <c r="O19" s="89"/>
+      <c r="P19" s="89"/>
+      <c r="Q19" s="89"/>
+      <c r="R19" s="89"/>
+      <c r="S19" s="89"/>
+      <c r="T19" s="89"/>
+      <c r="U19" s="89"/>
+      <c r="V19" s="89"/>
+      <c r="W19" s="89"/>
+      <c r="X19" s="89"/>
     </row>
     <row r="20" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A20" s="10" t="s">
@@ -6991,17 +7067,17 @@
       <c r="X21" s="6"/>
     </row>
     <row r="22" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="77" t="s">
+      <c r="A22" s="89" t="s">
         <v>357</v>
       </c>
-      <c r="B22" s="77"/>
-      <c r="C22" s="77"/>
-      <c r="D22" s="77"/>
-      <c r="E22" s="77"/>
-      <c r="F22" s="77"/>
-      <c r="G22" s="77"/>
-      <c r="H22" s="77"/>
-      <c r="I22" s="77"/>
+      <c r="B22" s="89"/>
+      <c r="C22" s="89"/>
+      <c r="D22" s="89"/>
+      <c r="E22" s="89"/>
+      <c r="F22" s="89"/>
+      <c r="G22" s="89"/>
+      <c r="H22" s="89"/>
+      <c r="I22" s="89"/>
       <c r="J22" s="6"/>
       <c r="K22" s="6"/>
       <c r="L22" s="6"/>
@@ -7249,32 +7325,32 @@
     </row>
     <row r="28" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.4"/>
     <row r="29" spans="1:33" s="7" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="79" t="s">
+      <c r="A29" s="88" t="s">
         <v>382</v>
       </c>
-      <c r="B29" s="77"/>
-      <c r="C29" s="77"/>
-      <c r="D29" s="77"/>
-      <c r="E29" s="77"/>
-      <c r="F29" s="77"/>
-      <c r="G29" s="77"/>
-      <c r="H29" s="77"/>
-      <c r="I29" s="77"/>
-      <c r="J29" s="77"/>
-      <c r="K29" s="77"/>
-      <c r="L29" s="77"/>
-      <c r="M29" s="77"/>
-      <c r="N29" s="77"/>
-      <c r="O29" s="77"/>
-      <c r="P29" s="77"/>
-      <c r="Q29" s="77"/>
-      <c r="R29" s="77"/>
-      <c r="S29" s="77"/>
-      <c r="T29" s="77"/>
-      <c r="U29" s="77"/>
-      <c r="V29" s="77"/>
-      <c r="W29" s="77"/>
-      <c r="X29" s="77"/>
+      <c r="B29" s="89"/>
+      <c r="C29" s="89"/>
+      <c r="D29" s="89"/>
+      <c r="E29" s="89"/>
+      <c r="F29" s="89"/>
+      <c r="G29" s="89"/>
+      <c r="H29" s="89"/>
+      <c r="I29" s="89"/>
+      <c r="J29" s="89"/>
+      <c r="K29" s="89"/>
+      <c r="L29" s="89"/>
+      <c r="M29" s="89"/>
+      <c r="N29" s="89"/>
+      <c r="O29" s="89"/>
+      <c r="P29" s="89"/>
+      <c r="Q29" s="89"/>
+      <c r="R29" s="89"/>
+      <c r="S29" s="89"/>
+      <c r="T29" s="89"/>
+      <c r="U29" s="89"/>
+      <c r="V29" s="89"/>
+      <c r="W29" s="89"/>
+      <c r="X29" s="89"/>
     </row>
     <row r="30" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A30" s="10" t="s">
@@ -7417,32 +7493,32 @@
     </row>
     <row r="34" spans="1:24" s="7" customFormat="1" x14ac:dyDescent="0.4"/>
     <row r="35" spans="1:24" x14ac:dyDescent="0.4">
-      <c r="A35" s="77" t="s">
+      <c r="A35" s="89" t="s">
         <v>390</v>
       </c>
-      <c r="B35" s="77"/>
-      <c r="C35" s="77"/>
-      <c r="D35" s="77"/>
-      <c r="E35" s="77"/>
-      <c r="F35" s="77"/>
-      <c r="G35" s="77"/>
-      <c r="H35" s="77"/>
-      <c r="I35" s="77"/>
-      <c r="J35" s="77"/>
-      <c r="K35" s="77"/>
-      <c r="L35" s="77"/>
-      <c r="M35" s="77"/>
-      <c r="N35" s="77"/>
-      <c r="O35" s="77"/>
-      <c r="P35" s="77"/>
-      <c r="Q35" s="77"/>
-      <c r="R35" s="77"/>
-      <c r="S35" s="77"/>
-      <c r="T35" s="77"/>
-      <c r="U35" s="77"/>
-      <c r="V35" s="77"/>
-      <c r="W35" s="77"/>
-      <c r="X35" s="77"/>
+      <c r="B35" s="89"/>
+      <c r="C35" s="89"/>
+      <c r="D35" s="89"/>
+      <c r="E35" s="89"/>
+      <c r="F35" s="89"/>
+      <c r="G35" s="89"/>
+      <c r="H35" s="89"/>
+      <c r="I35" s="89"/>
+      <c r="J35" s="89"/>
+      <c r="K35" s="89"/>
+      <c r="L35" s="89"/>
+      <c r="M35" s="89"/>
+      <c r="N35" s="89"/>
+      <c r="O35" s="89"/>
+      <c r="P35" s="89"/>
+      <c r="Q35" s="89"/>
+      <c r="R35" s="89"/>
+      <c r="S35" s="89"/>
+      <c r="T35" s="89"/>
+      <c r="U35" s="89"/>
+      <c r="V35" s="89"/>
+      <c r="W35" s="89"/>
+      <c r="X35" s="89"/>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A36" s="10" t="s">
@@ -7549,16 +7625,16 @@
       <c r="X37" s="5"/>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.4">
-      <c r="A38" s="77" t="s">
+      <c r="A38" s="89" t="s">
         <v>398</v>
       </c>
-      <c r="B38" s="77"/>
-      <c r="C38" s="77"/>
-      <c r="D38" s="77"/>
-      <c r="E38" s="77"/>
-      <c r="F38" s="77"/>
-      <c r="G38" s="77"/>
-      <c r="H38" s="77"/>
+      <c r="B38" s="89"/>
+      <c r="C38" s="89"/>
+      <c r="D38" s="89"/>
+      <c r="E38" s="89"/>
+      <c r="F38" s="89"/>
+      <c r="G38" s="89"/>
+      <c r="H38" s="89"/>
       <c r="I38" s="6"/>
       <c r="J38" s="6"/>
       <c r="K38" s="6"/>
@@ -7577,32 +7653,32 @@
       <c r="X38" s="5"/>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.4">
-      <c r="A40" s="80" t="s">
+      <c r="A40" s="91" t="s">
         <v>399</v>
       </c>
-      <c r="B40" s="80"/>
-      <c r="C40" s="80"/>
-      <c r="D40" s="80"/>
-      <c r="E40" s="80"/>
-      <c r="F40" s="80"/>
-      <c r="G40" s="80"/>
-      <c r="H40" s="80"/>
-      <c r="I40" s="80"/>
-      <c r="J40" s="80"/>
-      <c r="K40" s="80"/>
-      <c r="L40" s="80"/>
-      <c r="M40" s="80"/>
-      <c r="N40" s="80"/>
-      <c r="O40" s="80"/>
-      <c r="P40" s="80"/>
-      <c r="Q40" s="80"/>
-      <c r="R40" s="80"/>
-      <c r="S40" s="80"/>
-      <c r="T40" s="80"/>
-      <c r="U40" s="80"/>
-      <c r="V40" s="80"/>
-      <c r="W40" s="80"/>
-      <c r="X40" s="80"/>
+      <c r="B40" s="91"/>
+      <c r="C40" s="91"/>
+      <c r="D40" s="91"/>
+      <c r="E40" s="91"/>
+      <c r="F40" s="91"/>
+      <c r="G40" s="91"/>
+      <c r="H40" s="91"/>
+      <c r="I40" s="91"/>
+      <c r="J40" s="91"/>
+      <c r="K40" s="91"/>
+      <c r="L40" s="91"/>
+      <c r="M40" s="91"/>
+      <c r="N40" s="91"/>
+      <c r="O40" s="91"/>
+      <c r="P40" s="91"/>
+      <c r="Q40" s="91"/>
+      <c r="R40" s="91"/>
+      <c r="S40" s="91"/>
+      <c r="T40" s="91"/>
+      <c r="U40" s="91"/>
+      <c r="V40" s="91"/>
+      <c r="W40" s="91"/>
+      <c r="X40" s="91"/>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A41" s="16" t="s">
@@ -7689,16 +7765,16 @@
       <c r="X42" s="18"/>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.4">
-      <c r="A43" s="80" t="s">
+      <c r="A43" s="91" t="s">
         <v>404</v>
       </c>
-      <c r="B43" s="80"/>
-      <c r="C43" s="80"/>
-      <c r="D43" s="80"/>
-      <c r="E43" s="80"/>
-      <c r="F43" s="80"/>
-      <c r="G43" s="80"/>
-      <c r="H43" s="80"/>
+      <c r="B43" s="91"/>
+      <c r="C43" s="91"/>
+      <c r="D43" s="91"/>
+      <c r="E43" s="91"/>
+      <c r="F43" s="91"/>
+      <c r="G43" s="91"/>
+      <c r="H43" s="91"/>
       <c r="I43" s="19"/>
       <c r="J43" s="19"/>
       <c r="K43" s="19"/>
@@ -7731,32 +7807,32 @@
       <c r="M44" s="7"/>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.4">
-      <c r="A46" s="77" t="s">
+      <c r="A46" s="89" t="s">
         <v>405</v>
       </c>
-      <c r="B46" s="77"/>
-      <c r="C46" s="77"/>
-      <c r="D46" s="77"/>
-      <c r="E46" s="77"/>
-      <c r="F46" s="77"/>
-      <c r="G46" s="77"/>
-      <c r="H46" s="77"/>
-      <c r="I46" s="77"/>
-      <c r="J46" s="77"/>
-      <c r="K46" s="77"/>
-      <c r="L46" s="77"/>
-      <c r="M46" s="77"/>
-      <c r="N46" s="77"/>
-      <c r="O46" s="77"/>
-      <c r="P46" s="77"/>
-      <c r="Q46" s="77"/>
-      <c r="R46" s="77"/>
-      <c r="S46" s="77"/>
-      <c r="T46" s="77"/>
-      <c r="U46" s="77"/>
-      <c r="V46" s="77"/>
-      <c r="W46" s="77"/>
-      <c r="X46" s="77"/>
+      <c r="B46" s="89"/>
+      <c r="C46" s="89"/>
+      <c r="D46" s="89"/>
+      <c r="E46" s="89"/>
+      <c r="F46" s="89"/>
+      <c r="G46" s="89"/>
+      <c r="H46" s="89"/>
+      <c r="I46" s="89"/>
+      <c r="J46" s="89"/>
+      <c r="K46" s="89"/>
+      <c r="L46" s="89"/>
+      <c r="M46" s="89"/>
+      <c r="N46" s="89"/>
+      <c r="O46" s="89"/>
+      <c r="P46" s="89"/>
+      <c r="Q46" s="89"/>
+      <c r="R46" s="89"/>
+      <c r="S46" s="89"/>
+      <c r="T46" s="89"/>
+      <c r="U46" s="89"/>
+      <c r="V46" s="89"/>
+      <c r="W46" s="89"/>
+      <c r="X46" s="89"/>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.4">
       <c r="A47" s="10" t="s">
@@ -7843,16 +7919,16 @@
       <c r="X48" s="5"/>
     </row>
     <row r="49" spans="1:34" x14ac:dyDescent="0.4">
-      <c r="A49" s="77" t="s">
+      <c r="A49" s="89" t="s">
         <v>408</v>
       </c>
-      <c r="B49" s="77"/>
-      <c r="C49" s="77"/>
-      <c r="D49" s="77"/>
-      <c r="E49" s="77"/>
-      <c r="F49" s="77"/>
-      <c r="G49" s="77"/>
-      <c r="H49" s="77"/>
+      <c r="B49" s="89"/>
+      <c r="C49" s="89"/>
+      <c r="D49" s="89"/>
+      <c r="E49" s="89"/>
+      <c r="F49" s="89"/>
+      <c r="G49" s="89"/>
+      <c r="H49" s="89"/>
       <c r="I49" s="5"/>
       <c r="J49" s="5"/>
       <c r="K49" s="5"/>
@@ -7871,16 +7947,16 @@
       <c r="X49" s="5"/>
     </row>
     <row r="50" spans="1:34" x14ac:dyDescent="0.4">
-      <c r="A50" s="77" t="s">
+      <c r="A50" s="89" t="s">
         <v>409</v>
       </c>
-      <c r="B50" s="77"/>
-      <c r="C50" s="77"/>
-      <c r="D50" s="77"/>
-      <c r="E50" s="77"/>
-      <c r="F50" s="77"/>
-      <c r="G50" s="77"/>
-      <c r="H50" s="77"/>
+      <c r="B50" s="89"/>
+      <c r="C50" s="89"/>
+      <c r="D50" s="89"/>
+      <c r="E50" s="89"/>
+      <c r="F50" s="89"/>
+      <c r="G50" s="89"/>
+      <c r="H50" s="89"/>
       <c r="I50" s="5"/>
       <c r="J50" s="5"/>
       <c r="K50" s="5"/>
@@ -7899,32 +7975,32 @@
       <c r="X50" s="5"/>
     </row>
     <row r="52" spans="1:34" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="77" t="s">
+      <c r="A52" s="89" t="s">
         <v>410</v>
       </c>
-      <c r="B52" s="77"/>
-      <c r="C52" s="77"/>
-      <c r="D52" s="77"/>
-      <c r="E52" s="77"/>
-      <c r="F52" s="77"/>
-      <c r="G52" s="77"/>
-      <c r="H52" s="77"/>
-      <c r="I52" s="77"/>
-      <c r="J52" s="77"/>
-      <c r="K52" s="77"/>
-      <c r="L52" s="77"/>
-      <c r="M52" s="77"/>
-      <c r="N52" s="77"/>
-      <c r="O52" s="77"/>
-      <c r="P52" s="77"/>
-      <c r="Q52" s="77"/>
-      <c r="R52" s="77"/>
-      <c r="S52" s="77"/>
-      <c r="T52" s="77"/>
-      <c r="U52" s="77"/>
-      <c r="V52" s="77"/>
-      <c r="W52" s="77"/>
-      <c r="X52" s="78"/>
+      <c r="B52" s="89"/>
+      <c r="C52" s="89"/>
+      <c r="D52" s="89"/>
+      <c r="E52" s="89"/>
+      <c r="F52" s="89"/>
+      <c r="G52" s="89"/>
+      <c r="H52" s="89"/>
+      <c r="I52" s="89"/>
+      <c r="J52" s="89"/>
+      <c r="K52" s="89"/>
+      <c r="L52" s="89"/>
+      <c r="M52" s="89"/>
+      <c r="N52" s="89"/>
+      <c r="O52" s="89"/>
+      <c r="P52" s="89"/>
+      <c r="Q52" s="89"/>
+      <c r="R52" s="89"/>
+      <c r="S52" s="89"/>
+      <c r="T52" s="89"/>
+      <c r="U52" s="89"/>
+      <c r="V52" s="89"/>
+      <c r="W52" s="89"/>
+      <c r="X52" s="90"/>
     </row>
     <row r="53" spans="1:34" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A53" s="10" t="s">
@@ -8142,16 +8218,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="A3:X3"/>
-    <mergeCell ref="A6:R6"/>
-    <mergeCell ref="A7:R7"/>
-    <mergeCell ref="A9:X9"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A15:R15"/>
-    <mergeCell ref="A16:R16"/>
-    <mergeCell ref="A19:X19"/>
-    <mergeCell ref="A22:I22"/>
     <mergeCell ref="A46:X46"/>
     <mergeCell ref="A49:H49"/>
     <mergeCell ref="A50:H50"/>
@@ -8161,6 +8227,16 @@
     <mergeCell ref="A38:H38"/>
     <mergeCell ref="A40:X40"/>
     <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A15:R15"/>
+    <mergeCell ref="A16:R16"/>
+    <mergeCell ref="A19:X19"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A3:X3"/>
+    <mergeCell ref="A6:R6"/>
+    <mergeCell ref="A7:R7"/>
+    <mergeCell ref="A9:X9"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8179,11 +8255,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="92" t="s">
         <v>420</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="91"/>
+      <c r="B1" s="93"/>
+      <c r="C1" s="94"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
@@ -8192,7 +8268,7 @@
       <c r="B2" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="C2" s="92" t="s">
+      <c r="C2" s="95" t="s">
         <v>423</v>
       </c>
     </row>
@@ -8203,7 +8279,7 @@
       <c r="B3" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="C3" s="93"/>
+      <c r="C3" s="96"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
@@ -8221,7 +8297,7 @@
       <c r="B5" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="C5" s="76" t="s">
+      <c r="C5" s="79" t="s">
         <v>430</v>
       </c>
     </row>
@@ -8232,7 +8308,7 @@
       <c r="B6" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="C6" s="76"/>
+      <c r="C6" s="79"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
@@ -8241,7 +8317,7 @@
       <c r="B7" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="C7" s="76" t="s">
+      <c r="C7" s="79" t="s">
         <v>435</v>
       </c>
     </row>
@@ -8252,7 +8328,7 @@
       <c r="B8" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="C8" s="76"/>
+      <c r="C8" s="79"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" s="3" t="s">
